--- a/raw_data/cost_data_collection.xlsx
+++ b/raw_data/cost_data_collection.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30516"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{55BEFA44-F5E8-4583-8C97-582736C20BAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1d83fea8a85e4500/Documents/JJE/RS/biogas-upgrading-project/raw_data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="37" documentId="8_{55BEFA44-F5E8-4583-8C97-582736C20BAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{523B1827-614E-4E1D-A17B-A8B9284ECE08}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Read Me" sheetId="3" r:id="rId1"/>
@@ -38,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1173" uniqueCount="273">
   <si>
     <t>Sheet Name</t>
   </si>
@@ -358,12 +363,6 @@
     <t>status</t>
   </si>
   <si>
-    <t>Example</t>
-  </si>
-  <si>
-    <t>USD_2015</t>
-  </si>
-  <si>
     <t>m3_per_hr</t>
   </si>
   <si>
@@ -565,18 +564,9 @@
     <t>Persson et al. 2006</t>
   </si>
   <si>
-    <t>SEK</t>
-  </si>
-  <si>
     <t>Not specified</t>
   </si>
   <si>
-    <t>READ FROM PLOT - unnumbered 'Investment cost' scatter graph, printed page 25 (PDF page 13, right-hand page of the two-page spread). One of 16 Swedish upgrading plants; marker position read against the graph's gridlines and axis labels. The graph does not identify each plant's technology. The report states the investments were made between 1998 and 2006 and does not say they were adjusted to a common year. Building not included for most plants. Source image is low resolution (each marker ~2 original pixels), so precision is about +/-0.35 MSEK and +/-12 Nm3/h. 15 of the 16 markers are separable; one overlaps another.</t>
-  </si>
-  <si>
-    <t>READ FROM PLOT - unnumbered 'Investment cost' scatter graph, printed page 25 (PDF page 13, right-hand page of the two-page spread). One of 16 Swedish upgrading plants; marker position read against the graph's gridlines and axis labels. The graph does not identify each plant's technology. The report states the investments were made between 1998 and 2006 and does not say they were adjusted to a common year. Building not included for most plants. Source image is low resolution (each marker ~2 original pixels), so precision is about +/-0.35 MSEK and +/-12 Nm3/h. 15 of the 16 markers are separable; one overlaps another. This marker overlapped a neighbour and was separated by position.</t>
-  </si>
-  <si>
     <t>FROM TEXT (not a plot) - 'Cost of upgrading' section, printed page 25 (PDF page 13). Persson et al. 2006, 'Cost of upgrading' (stated in text): typical investment for a plant treating 300 nm3/h of raw gas is in the order of 1 million EUR, for full treatment to vehicle fuel quality. Land not included.</t>
   </si>
   <si>
@@ -613,9 +603,6 @@
     <t>2007-2008</t>
   </si>
   <si>
-    <t>Checked</t>
-  </si>
-  <si>
     <t>FROM TEXT/TABLE (not a plot) - Table 5-6, page 93 (PDF page 93). Malmberg pressurised water scrubbing, turnkey; breakdown: plant 900,000 + off-gas treatment 200,000 + ancillary construction 45,000. Includes adsorption gas drying, any fine desulphurisation, and thermal off-gas oxidation (Vocsidizer/VocsiBox). Standard modules GR3L/GR6L/GR12L have spare capacity (up to 300/600/1,250 Nm3/h). Product gas assumes 1% methane loss. Price basis: the report states all investment and operating costs were obtained directly from the suppliers between 2007 and 2008 (p. 84); indicative prices, net before taxes; transport, installation and commissioning included unless stated; rounded up to full 1,000 EUR. Capacity = raw biogas. Product gas figure is the report's own, taken from the same table.</t>
   </si>
   <si>
@@ -872,6 +859,9 @@
   </si>
   <si>
     <t>Soko&amp;Andersen 2025.pdf</t>
+  </si>
+  <si>
+    <t>checked</t>
   </si>
 </sst>
 </file>
@@ -883,7 +873,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1047,10 +1037,14 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1088,7 +1082,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1194,7 +1188,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1336,7 +1330,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1345,13 +1339,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B66E1F6-965F-4D4A-9CFE-22FBD5AEDE12}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="65.5703125" customWidth="1"/>
+    <col min="1" max="1" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1359,7 +1353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="45.75">
+    <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1367,7 +1361,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="60.75">
+    <row r="3" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1383,30 +1377,30 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X33"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16" style="11" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="29.140625" customWidth="1"/>
-    <col min="6" max="6" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.140625" customWidth="1"/>
-    <col min="8" max="8" width="16.85546875" customWidth="1"/>
-    <col min="9" max="9" width="31.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.109375" customWidth="1"/>
+    <col min="6" max="6" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.109375" customWidth="1"/>
+    <col min="8" max="8" width="16.88671875" customWidth="1"/>
+    <col min="9" max="9" width="31.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.33203125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="24" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="24.28515625" customWidth="1"/>
+    <col min="13" max="13" width="24.33203125" customWidth="1"/>
     <col min="14" max="14" width="40" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="40" customWidth="1"/>
-    <col min="16" max="16" width="24.28515625" customWidth="1"/>
-    <col min="17" max="17" width="28.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="23" width="28.42578125" customWidth="1"/>
-    <col min="24" max="24" width="59.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="24.33203125" customWidth="1"/>
+    <col min="17" max="17" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="23" width="28.44140625" customWidth="1"/>
+    <col min="24" max="24" width="59.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1">
+    <row r="1" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -1480,7 +1474,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>27</v>
       </c>
@@ -1513,7 +1507,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:24" ht="45.75">
+    <row r="3" spans="1:24" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>34</v>
       </c>
@@ -1536,7 +1530,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:24" ht="45.75">
+    <row r="4" spans="1:24" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>34</v>
       </c>
@@ -1559,7 +1553,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="45.75">
+    <row r="5" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>34</v>
       </c>
@@ -1588,7 +1582,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>34</v>
       </c>
@@ -1611,7 +1605,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>34</v>
       </c>
@@ -1634,7 +1628,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="45.75">
+    <row r="8" spans="1:24" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>44</v>
       </c>
@@ -1681,7 +1675,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="45.75">
+    <row r="9" spans="1:24" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C9" s="11">
         <v>1400000</v>
       </c>
@@ -1719,7 +1713,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:24" ht="45.75">
+    <row r="10" spans="1:24" ht="43.2" x14ac:dyDescent="0.3">
       <c r="J10">
         <v>0.2</v>
       </c>
@@ -1730,7 +1724,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="60.75">
+    <row r="11" spans="1:24" ht="57.6" x14ac:dyDescent="0.3">
       <c r="J11">
         <v>0.17</v>
       </c>
@@ -1741,7 +1735,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="48.75" customHeight="1">
+    <row r="12" spans="1:24" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="J12">
         <v>0.25</v>
       </c>
@@ -1752,7 +1746,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="48.75" customHeight="1">
+    <row r="13" spans="1:24" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="J13">
         <v>0.3</v>
       </c>
@@ -1763,7 +1757,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>44</v>
       </c>
@@ -1808,7 +1802,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="H15" t="s">
         <v>66</v>
       </c>
@@ -1831,7 +1825,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="30.75">
+    <row r="16" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
       <c r="H16" t="s">
         <v>67</v>
       </c>
@@ -1848,7 +1842,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="17" spans="1:23" ht="30.75">
+    <row r="17" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="J17">
         <v>0.05</v>
       </c>
@@ -1859,7 +1853,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:23">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>44</v>
       </c>
@@ -1897,7 +1891,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="19" spans="1:23">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
       <c r="J19">
         <v>0.3</v>
       </c>
@@ -1923,7 +1917,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="20" spans="1:23" ht="30.75">
+    <row r="20" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>44</v>
       </c>
@@ -1976,7 +1970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:23" ht="30.75">
+    <row r="21" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="J21">
         <v>0.15</v>
       </c>
@@ -2005,7 +1999,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="22" spans="1:23" ht="30.75">
+    <row r="22" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="J22">
         <v>0.05</v>
       </c>
@@ -2028,7 +2022,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="23" spans="1:23" ht="30.75">
+    <row r="23" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="J23">
         <v>0.1</v>
       </c>
@@ -2051,7 +2045,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="24" spans="1:23" ht="30.75">
+    <row r="24" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="J24">
         <v>0.01</v>
       </c>
@@ -2071,7 +2065,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="25" spans="1:23" ht="30.75">
+    <row r="25" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="J25">
         <v>0.05</v>
       </c>
@@ -2091,7 +2085,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="26" spans="1:23">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
       <c r="H26" s="17">
         <v>400</v>
       </c>
@@ -2115,7 +2109,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="27" spans="1:23">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
       <c r="H27" s="17">
         <v>2000</v>
       </c>
@@ -2138,7 +2132,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="28" spans="1:23" ht="30.75">
+    <row r="28" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C28" s="11">
         <v>380000</v>
       </c>
@@ -2171,7 +2165,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:23">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
       <c r="H29" s="15"/>
       <c r="I29" s="15"/>
       <c r="J29" s="15">
@@ -2191,7 +2185,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:23" ht="30.75">
+    <row r="30" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C30" s="11">
         <v>360000</v>
       </c>
@@ -2224,7 +2218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:23" ht="30.75">
+    <row r="31" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C31" s="11">
         <v>460000</v>
       </c>
@@ -2247,7 +2241,7 @@
       </c>
       <c r="N31" s="12"/>
     </row>
-    <row r="32" spans="1:23">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>44</v>
       </c>
@@ -2267,7 +2261,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="33" spans="18:19">
+    <row r="33" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R33">
         <v>98</v>
       </c>
@@ -2282,26 +2276,26 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{925FD099-4F54-45E9-9EF1-2DAB6BE6BFFA}">
-  <dimension ref="A1:N128"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:M112"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.140625" style="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.5703125" style="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.85546875" style="18" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="26.140625" style="21" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29.42578125" style="15" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="29.42578125" style="22" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="26.140625" style="20" customWidth="1"/>
-    <col min="11" max="11" width="50.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="67.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="67.42578125" customWidth="1"/>
+    <col min="1" max="1" width="25.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.109375" style="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.5546875" style="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.33203125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.44140625" style="18" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21" style="18" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.88671875" style="15" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="26.88671875" style="22" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.77734375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="50.88671875" customWidth="1"/>
+    <col min="12" max="12" width="8.5546875" customWidth="1"/>
+    <col min="13" max="13" width="67.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="67.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>94</v>
       </c>
@@ -2342,3852 +2336,3589 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>106</v>
+        <v>44</v>
       </c>
       <c r="B2" s="19">
-        <v>1790000</v>
+        <v>5086</v>
       </c>
       <c r="C2" s="18" t="s">
         <v>107</v>
       </c>
       <c r="E2" s="18">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="F2" s="18" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="H2" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="I2" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="K2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L2" t="s">
+        <v>272</v>
+      </c>
+      <c r="M2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>44</v>
       </c>
       <c r="B3" s="19">
-        <v>5086</v>
+        <v>4042</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E3" s="18">
-        <v>130</v>
+        <v>250</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I3" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K3" t="s">
         <v>72</v>
       </c>
+      <c r="L3" t="s">
+        <v>272</v>
+      </c>
       <c r="M3" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>44</v>
       </c>
       <c r="B4" s="19">
-        <v>4042</v>
+        <v>2595</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E4" s="18">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I4" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K4" t="s">
         <v>72</v>
       </c>
+      <c r="L4" t="s">
+        <v>272</v>
+      </c>
       <c r="M4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>44</v>
       </c>
       <c r="B5" s="19">
-        <v>2595</v>
+        <v>1930</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E5" s="18">
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I5" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K5" t="s">
         <v>72</v>
       </c>
+      <c r="L5" t="s">
+        <v>272</v>
+      </c>
       <c r="M5" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>44</v>
       </c>
       <c r="B6" s="19">
-        <v>1930</v>
+        <v>1694</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E6" s="18">
-        <v>750</v>
+        <v>1000</v>
       </c>
       <c r="F6" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H6" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I6" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K6" t="s">
         <v>72</v>
       </c>
+      <c r="L6" t="s">
+        <v>272</v>
+      </c>
       <c r="M6" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>44</v>
       </c>
       <c r="B7" s="19">
-        <v>1694</v>
+        <v>1626</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E7" s="18">
-        <v>1000</v>
+        <v>1250</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I7" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K7" t="s">
         <v>72</v>
       </c>
+      <c r="L7" t="s">
+        <v>272</v>
+      </c>
       <c r="M7" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>44</v>
       </c>
       <c r="B8" s="19">
-        <v>1626</v>
+        <v>1580</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E8" s="18">
-        <v>1250</v>
+        <v>1500</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I8" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K8" t="s">
         <v>72</v>
       </c>
+      <c r="L8" t="s">
+        <v>272</v>
+      </c>
       <c r="M8" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>44</v>
       </c>
       <c r="B9" s="19">
-        <v>1580</v>
+        <v>1501</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E9" s="18">
-        <v>1500</v>
+        <v>1750</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I9" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K9" t="s">
         <v>72</v>
       </c>
+      <c r="L9" t="s">
+        <v>272</v>
+      </c>
       <c r="M9" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>44</v>
       </c>
       <c r="B10" s="19">
-        <v>1501</v>
+        <v>1426</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E10" s="18">
-        <v>1750</v>
+        <v>2000</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I10" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K10" t="s">
         <v>72</v>
       </c>
+      <c r="L10" t="s">
+        <v>272</v>
+      </c>
       <c r="M10" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>44</v>
       </c>
       <c r="B11" s="19">
-        <v>1426</v>
+        <v>2819</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E11" s="18">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I11" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K11" t="s">
-        <v>72</v>
+        <v>119</v>
+      </c>
+      <c r="L11" t="s">
+        <v>272</v>
       </c>
       <c r="M11" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>44</v>
       </c>
       <c r="B12" s="19">
-        <v>2819</v>
+        <v>2333</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E12" s="18">
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I12" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K12" t="s">
+        <v>119</v>
+      </c>
+      <c r="L12" t="s">
+        <v>272</v>
+      </c>
+      <c r="M12" t="s">
         <v>121</v>
       </c>
-      <c r="M12" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>44</v>
       </c>
       <c r="B13" s="19">
-        <v>2333</v>
+        <v>2037</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E13" s="18">
-        <v>750</v>
+        <v>1000</v>
       </c>
       <c r="F13" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I13" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K13" t="s">
-        <v>121</v>
+        <v>119</v>
+      </c>
+      <c r="L13" t="s">
+        <v>272</v>
       </c>
       <c r="M13" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>44</v>
       </c>
       <c r="B14" s="19">
-        <v>2037</v>
+        <v>1833</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E14" s="18">
-        <v>1000</v>
+        <v>1250</v>
       </c>
       <c r="F14" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H14" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I14" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K14" t="s">
-        <v>121</v>
+        <v>119</v>
+      </c>
+      <c r="L14" t="s">
+        <v>272</v>
       </c>
       <c r="M14" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>44</v>
       </c>
       <c r="B15" s="19">
-        <v>1833</v>
+        <v>1684</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E15" s="18">
-        <v>1250</v>
+        <v>1500</v>
       </c>
       <c r="F15" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I15" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K15" t="s">
-        <v>121</v>
+        <v>119</v>
+      </c>
+      <c r="L15" t="s">
+        <v>272</v>
       </c>
       <c r="M15" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>44</v>
       </c>
       <c r="B16" s="19">
-        <v>1684</v>
+        <v>1566</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E16" s="18">
-        <v>1500</v>
+        <v>1750</v>
       </c>
       <c r="F16" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H16" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I16" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K16" t="s">
-        <v>121</v>
+        <v>119</v>
+      </c>
+      <c r="L16" t="s">
+        <v>272</v>
       </c>
       <c r="M16" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>44</v>
       </c>
       <c r="B17" s="19">
-        <v>1566</v>
+        <v>1471</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E17" s="18">
-        <v>1750</v>
+        <v>2000</v>
       </c>
       <c r="F17" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H17" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I17" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K17" t="s">
-        <v>121</v>
+        <v>119</v>
+      </c>
+      <c r="L17" t="s">
+        <v>272</v>
       </c>
       <c r="M17" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>44</v>
       </c>
       <c r="B18" s="19">
-        <v>1471</v>
+        <v>4949</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E18" s="18">
-        <v>2000</v>
+        <v>140</v>
       </c>
       <c r="F18" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H18" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I18" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K18" t="s">
-        <v>121</v>
+        <v>127</v>
+      </c>
+      <c r="L18" t="s">
+        <v>272</v>
       </c>
       <c r="M18" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>44</v>
       </c>
       <c r="B19" s="19">
-        <v>4949</v>
+        <v>3861</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E19" s="18">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="F19" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H19" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I19" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K19" t="s">
+        <v>127</v>
+      </c>
+      <c r="L19" t="s">
+        <v>272</v>
+      </c>
+      <c r="M19" t="s">
         <v>129</v>
       </c>
-      <c r="M19" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>44</v>
       </c>
       <c r="B20" s="19">
-        <v>3861</v>
+        <v>2722</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E20" s="18">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="F20" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H20" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I20" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K20" t="s">
-        <v>129</v>
+        <v>127</v>
+      </c>
+      <c r="L20" t="s">
+        <v>272</v>
       </c>
       <c r="M20" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>44</v>
       </c>
       <c r="B21" s="19">
-        <v>2722</v>
+        <v>2392</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E21" s="18">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="F21" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H21" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I21" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K21" t="s">
-        <v>129</v>
+        <v>127</v>
+      </c>
+      <c r="L21" t="s">
+        <v>272</v>
       </c>
       <c r="M21" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>44</v>
       </c>
       <c r="B22" s="19">
-        <v>2392</v>
+        <v>2074</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E22" s="18">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="F22" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H22" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I22" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K22" t="s">
-        <v>129</v>
+        <v>127</v>
+      </c>
+      <c r="L22" t="s">
+        <v>272</v>
       </c>
       <c r="M22" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>44</v>
       </c>
       <c r="B23" s="19">
-        <v>2074</v>
+        <v>1943</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E23" s="18">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H23" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I23" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K23" t="s">
-        <v>129</v>
+        <v>127</v>
+      </c>
+      <c r="L23" t="s">
+        <v>272</v>
       </c>
       <c r="M23" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>44</v>
       </c>
       <c r="B24" s="19">
-        <v>1943</v>
+        <v>1917</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E24" s="18">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="F24" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H24" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I24" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K24" t="s">
-        <v>129</v>
+        <v>127</v>
+      </c>
+      <c r="L24" t="s">
+        <v>272</v>
       </c>
       <c r="M24" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>44</v>
       </c>
       <c r="B25" s="19">
-        <v>1917</v>
+        <v>1829</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E25" s="18">
-        <v>1200</v>
+        <v>1400</v>
       </c>
       <c r="F25" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H25" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I25" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K25" t="s">
-        <v>129</v>
+        <v>127</v>
+      </c>
+      <c r="L25" t="s">
+        <v>272</v>
       </c>
       <c r="M25" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>44</v>
       </c>
       <c r="B26" s="19">
-        <v>1829</v>
+        <v>3191</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E26" s="18">
-        <v>1400</v>
+        <v>600</v>
       </c>
       <c r="F26" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H26" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I26" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K26" t="s">
-        <v>129</v>
+        <v>136</v>
+      </c>
+      <c r="L26" t="s">
+        <v>272</v>
       </c>
       <c r="M26" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>44</v>
       </c>
       <c r="B27" s="19">
-        <v>3191</v>
+        <v>2799</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E27" s="18">
-        <v>600</v>
+        <v>750</v>
       </c>
       <c r="F27" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H27" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I27" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K27" t="s">
+        <v>136</v>
+      </c>
+      <c r="L27" t="s">
+        <v>272</v>
+      </c>
+      <c r="M27" t="s">
         <v>138</v>
       </c>
-      <c r="M27" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13">
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>44</v>
       </c>
       <c r="B28" s="19">
-        <v>2799</v>
+        <v>2399</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E28" s="18">
-        <v>750</v>
+        <v>1000</v>
       </c>
       <c r="F28" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H28" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I28" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K28" t="s">
-        <v>138</v>
+        <v>136</v>
+      </c>
+      <c r="L28" t="s">
+        <v>272</v>
       </c>
       <c r="M28" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>44</v>
       </c>
       <c r="B29" s="19">
-        <v>2399</v>
+        <v>2132</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E29" s="18">
-        <v>1000</v>
+        <v>1250</v>
       </c>
       <c r="F29" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H29" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I29" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K29" t="s">
-        <v>138</v>
+        <v>136</v>
+      </c>
+      <c r="L29" t="s">
+        <v>272</v>
       </c>
       <c r="M29" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>44</v>
       </c>
       <c r="B30" s="19">
-        <v>2132</v>
+        <v>1887</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E30" s="18">
-        <v>1250</v>
+        <v>1500</v>
       </c>
       <c r="F30" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H30" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I30" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K30" t="s">
-        <v>138</v>
+        <v>136</v>
+      </c>
+      <c r="L30" t="s">
+        <v>272</v>
       </c>
       <c r="M30" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>44</v>
       </c>
       <c r="B31" s="19">
-        <v>1887</v>
+        <v>1637</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E31" s="18">
-        <v>1500</v>
+        <v>1750</v>
       </c>
       <c r="F31" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H31" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I31" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K31" t="s">
-        <v>138</v>
+        <v>136</v>
+      </c>
+      <c r="L31" t="s">
+        <v>272</v>
       </c>
       <c r="M31" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>44</v>
       </c>
       <c r="B32" s="19">
-        <v>1637</v>
+        <v>1594</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E32" s="18">
-        <v>1750</v>
+        <v>1800</v>
       </c>
       <c r="F32" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H32" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I32" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K32" t="s">
-        <v>138</v>
+        <v>136</v>
+      </c>
+      <c r="L32" t="s">
+        <v>272</v>
       </c>
       <c r="M32" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>44</v>
       </c>
       <c r="B33" s="19">
-        <v>1594</v>
+        <v>4380</v>
       </c>
       <c r="C33" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E33" s="18">
-        <v>1800</v>
+        <v>250</v>
       </c>
       <c r="F33" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H33" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I33" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K33" t="s">
-        <v>138</v>
+        <v>144</v>
+      </c>
+      <c r="L33" t="s">
+        <v>272</v>
       </c>
       <c r="M33" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="34" spans="1:13">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>44</v>
       </c>
       <c r="B34" s="19">
-        <v>4380</v>
+        <v>3287</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E34" s="18">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="F34" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H34" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I34" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K34" t="s">
+        <v>144</v>
+      </c>
+      <c r="L34" t="s">
+        <v>272</v>
+      </c>
+      <c r="M34" t="s">
         <v>146</v>
       </c>
-      <c r="M34" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13">
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>44</v>
       </c>
       <c r="B35" s="19">
-        <v>3287</v>
+        <v>2573</v>
       </c>
       <c r="C35" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E35" s="18">
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="F35" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H35" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I35" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K35" t="s">
-        <v>146</v>
+        <v>144</v>
+      </c>
+      <c r="L35" t="s">
+        <v>272</v>
       </c>
       <c r="M35" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>44</v>
       </c>
       <c r="B36" s="19">
-        <v>2573</v>
+        <v>2113</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E36" s="18">
-        <v>750</v>
+        <v>1000</v>
       </c>
       <c r="F36" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H36" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I36" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K36" t="s">
-        <v>146</v>
+        <v>144</v>
+      </c>
+      <c r="L36" t="s">
+        <v>272</v>
       </c>
       <c r="M36" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>44</v>
       </c>
       <c r="B37" s="19">
-        <v>2113</v>
+        <v>1817</v>
       </c>
       <c r="C37" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E37" s="18">
-        <v>1000</v>
+        <v>1250</v>
       </c>
       <c r="F37" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H37" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I37" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K37" t="s">
-        <v>146</v>
+        <v>144</v>
+      </c>
+      <c r="L37" t="s">
+        <v>272</v>
       </c>
       <c r="M37" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>44</v>
       </c>
       <c r="B38" s="19">
-        <v>1817</v>
+        <v>1623</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E38" s="18">
-        <v>1250</v>
+        <v>1500</v>
       </c>
       <c r="F38" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H38" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I38" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K38" t="s">
-        <v>146</v>
+        <v>144</v>
+      </c>
+      <c r="L38" t="s">
+        <v>272</v>
       </c>
       <c r="M38" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>44</v>
       </c>
       <c r="B39" s="19">
-        <v>1623</v>
+        <v>1497</v>
       </c>
       <c r="C39" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E39" s="18">
-        <v>1500</v>
+        <v>1750</v>
       </c>
       <c r="F39" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H39" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I39" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K39" t="s">
-        <v>146</v>
+        <v>144</v>
+      </c>
+      <c r="L39" t="s">
+        <v>272</v>
       </c>
       <c r="M39" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>44</v>
       </c>
       <c r="B40" s="19">
-        <v>1497</v>
+        <v>1453</v>
       </c>
       <c r="C40" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E40" s="18">
-        <v>1750</v>
+        <v>2000</v>
       </c>
       <c r="F40" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H40" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I40" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K40" t="s">
-        <v>146</v>
+        <v>144</v>
+      </c>
+      <c r="L40" t="s">
+        <v>272</v>
       </c>
       <c r="M40" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>44</v>
       </c>
       <c r="B41" s="19">
-        <v>1453</v>
+        <v>1100000</v>
       </c>
       <c r="C41" s="18" t="s">
-        <v>109</v>
+        <v>153</v>
       </c>
       <c r="E41" s="18">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="F41" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H41" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I41" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K41" t="s">
-        <v>146</v>
+        <v>119</v>
+      </c>
+      <c r="L41" t="s">
+        <v>272</v>
       </c>
       <c r="M41" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="42" spans="1:13">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>44</v>
       </c>
       <c r="B42" s="19">
-        <v>1100000</v>
+        <v>1400000</v>
       </c>
       <c r="C42" s="18" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E42" s="18">
         <v>500</v>
       </c>
       <c r="F42" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H42" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I42" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K42" t="s">
-        <v>121</v>
+        <v>119</v>
+      </c>
+      <c r="L42" t="s">
+        <v>272</v>
       </c>
       <c r="M42" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>44</v>
       </c>
       <c r="B43" s="19">
-        <v>1400000</v>
+        <v>380000</v>
       </c>
       <c r="C43" s="18" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E43" s="18">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="F43" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H43" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I43" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K43" t="s">
-        <v>121</v>
+        <v>156</v>
+      </c>
+      <c r="L43" t="s">
+        <v>272</v>
       </c>
       <c r="M43" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="44" spans="1:13">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>44</v>
       </c>
       <c r="B44" s="19">
-        <v>380000</v>
+        <v>360000</v>
       </c>
       <c r="C44" s="18" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E44" s="18">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="F44" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H44" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I44" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K44" t="s">
         <v>158</v>
       </c>
+      <c r="L44" t="s">
+        <v>272</v>
+      </c>
       <c r="M44" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="45" spans="1:13">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>44</v>
       </c>
       <c r="B45" s="19">
-        <v>360000</v>
+        <v>460000</v>
       </c>
       <c r="C45" s="18" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E45" s="18">
         <v>72</v>
       </c>
       <c r="F45" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H45" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I45" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K45" t="s">
+        <v>158</v>
+      </c>
+      <c r="L45" t="s">
+        <v>272</v>
+      </c>
+      <c r="M45" t="s">
         <v>160</v>
       </c>
-      <c r="M45" t="s">
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="46" spans="1:13">
-      <c r="A46" t="s">
-        <v>44</v>
-      </c>
       <c r="B46" s="19">
-        <v>460000</v>
+        <v>112000</v>
       </c>
       <c r="C46" s="18" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="E46" s="18">
-        <v>72</v>
+        <v>298</v>
       </c>
       <c r="F46" s="18" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H46" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I46" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K46" t="s">
-        <v>160</v>
+        <v>127</v>
+      </c>
+      <c r="L46" t="s">
+        <v>272</v>
       </c>
       <c r="M46" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>161</v>
+      </c>
+      <c r="B47" s="19">
+        <v>69800</v>
+      </c>
+      <c r="C47" s="18" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="47" spans="1:13">
-      <c r="A47" t="s">
+      <c r="E47" s="18">
+        <v>373</v>
+      </c>
+      <c r="F47" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="H47" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="I47" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="K47" t="s">
+        <v>127</v>
+      </c>
+      <c r="L47" t="s">
+        <v>272</v>
+      </c>
+      <c r="M47" t="s">
         <v>163</v>
       </c>
-      <c r="B47" s="19">
-        <v>112000</v>
-      </c>
-      <c r="C47" s="18" t="s">
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>161</v>
+      </c>
+      <c r="B48" s="19">
+        <v>87700</v>
+      </c>
+      <c r="C48" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="E48" s="18">
+        <v>398</v>
+      </c>
+      <c r="F48" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="H48" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="I48" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="K48" t="s">
+        <v>127</v>
+      </c>
+      <c r="L48" t="s">
+        <v>272</v>
+      </c>
+      <c r="M48" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>161</v>
+      </c>
+      <c r="B49" s="19">
+        <v>43100</v>
+      </c>
+      <c r="C49" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="E49" s="18">
+        <v>622</v>
+      </c>
+      <c r="F49" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="H49" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="I49" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="K49" t="s">
+        <v>127</v>
+      </c>
+      <c r="L49" t="s">
+        <v>272</v>
+      </c>
+      <c r="M49" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>161</v>
+      </c>
+      <c r="B50" s="19">
+        <v>80000</v>
+      </c>
+      <c r="C50" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="E50" s="18">
+        <v>997</v>
+      </c>
+      <c r="F50" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="H50" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="I50" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="K50" t="s">
+        <v>127</v>
+      </c>
+      <c r="L50" t="s">
+        <v>272</v>
+      </c>
+      <c r="M50" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>161</v>
+      </c>
+      <c r="B51" s="19">
+        <v>56700</v>
+      </c>
+      <c r="C51" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="E51" s="18">
+        <v>1597</v>
+      </c>
+      <c r="F51" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="H51" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="I51" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="K51" t="s">
+        <v>127</v>
+      </c>
+      <c r="L51" t="s">
+        <v>272</v>
+      </c>
+      <c r="M51" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>161</v>
+      </c>
+      <c r="B52" s="19">
+        <v>1240000</v>
+      </c>
+      <c r="C52" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="E52" s="18">
+        <v>800</v>
+      </c>
+      <c r="F52" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="H52" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="I52" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="K52" t="s">
+        <v>119</v>
+      </c>
+      <c r="L52" t="s">
+        <v>272</v>
+      </c>
+      <c r="M52" t="s">
         <v>164</v>
       </c>
-      <c r="E47" s="18">
-        <v>298</v>
-      </c>
-      <c r="F47" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="H47" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="I47" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="K47" t="s">
-        <v>129</v>
-      </c>
-      <c r="M47" t="s">
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>161</v>
+      </c>
+      <c r="B53" s="19">
+        <v>860000</v>
+      </c>
+      <c r="C53" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="E53" s="18">
+        <v>200</v>
+      </c>
+      <c r="F53" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="H53" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="I53" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="K53" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="48" spans="1:13">
-      <c r="A48" t="s">
-        <v>163</v>
-      </c>
-      <c r="B48" s="19">
-        <v>69800</v>
-      </c>
-      <c r="C48" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="E48" s="18">
-        <v>373</v>
-      </c>
-      <c r="F48" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="H48" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="I48" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="K48" t="s">
-        <v>129</v>
-      </c>
-      <c r="M48" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13">
-      <c r="A49" t="s">
-        <v>163</v>
-      </c>
-      <c r="B49" s="19">
-        <v>87700</v>
-      </c>
-      <c r="C49" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="E49" s="18">
-        <v>398</v>
-      </c>
-      <c r="F49" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="H49" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="I49" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="K49" t="s">
-        <v>129</v>
-      </c>
-      <c r="M49" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13">
-      <c r="A50" t="s">
-        <v>163</v>
-      </c>
-      <c r="B50" s="19">
-        <v>43100</v>
-      </c>
-      <c r="C50" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="E50" s="18">
-        <v>622</v>
-      </c>
-      <c r="F50" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="H50" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="I50" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="K50" t="s">
-        <v>129</v>
-      </c>
-      <c r="M50" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13">
-      <c r="A51" t="s">
-        <v>163</v>
-      </c>
-      <c r="B51" s="19">
-        <v>80000</v>
-      </c>
-      <c r="C51" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="E51" s="18">
-        <v>997</v>
-      </c>
-      <c r="F51" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="H51" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="I51" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="K51" t="s">
-        <v>129</v>
-      </c>
-      <c r="M51" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13">
-      <c r="A52" t="s">
-        <v>163</v>
-      </c>
-      <c r="B52" s="19">
-        <v>56700</v>
-      </c>
-      <c r="C52" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="E52" s="18">
-        <v>1597</v>
-      </c>
-      <c r="F52" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="H52" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="I52" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="K52" t="s">
-        <v>129</v>
-      </c>
-      <c r="M52" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13">
-      <c r="A53" t="s">
-        <v>163</v>
-      </c>
-      <c r="B53" s="19">
-        <v>1240000</v>
-      </c>
-      <c r="C53" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="E53" s="18">
-        <v>800</v>
-      </c>
-      <c r="F53" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="H53" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="I53" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="K53" t="s">
-        <v>121</v>
+      <c r="L53" t="s">
+        <v>272</v>
       </c>
       <c r="M53" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="54" spans="1:13">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B54" s="19">
-        <v>860000</v>
+        <v>2500000</v>
       </c>
       <c r="C54" s="18" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E54" s="18">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="F54" s="18" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H54" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I54" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K54" t="s">
+        <v>165</v>
+      </c>
+      <c r="L54" t="s">
+        <v>272</v>
+      </c>
+      <c r="M54" t="s">
         <v>167</v>
       </c>
-      <c r="M54" t="s">
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>161</v>
+      </c>
+      <c r="B55" s="19">
+        <v>39000</v>
+      </c>
+      <c r="C55" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="E55" s="18">
+        <v>400</v>
+      </c>
+      <c r="F55" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="H55" s="15">
+        <v>1980000</v>
+      </c>
+      <c r="I55" s="22" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="55" spans="1:13">
-      <c r="A55" t="s">
-        <v>163</v>
-      </c>
-      <c r="B55" s="19">
-        <v>2500000</v>
-      </c>
-      <c r="C55" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="E55" s="18">
-        <v>660</v>
-      </c>
-      <c r="F55" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="H55" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="I55" s="22" t="s">
-        <v>111</v>
-      </c>
       <c r="K55" t="s">
-        <v>167</v>
+        <v>169</v>
+      </c>
+      <c r="L55" t="s">
+        <v>272</v>
       </c>
       <c r="M55" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>161</v>
+      </c>
+      <c r="B56" s="19">
+        <v>81000</v>
+      </c>
+      <c r="C56" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="E56" s="18">
+        <v>1600</v>
+      </c>
+      <c r="F56" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="H56" s="15">
+        <v>7910000</v>
+      </c>
+      <c r="I56" s="22" t="s">
+        <v>168</v>
+      </c>
+      <c r="K56" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="56" spans="1:13">
-      <c r="A56" t="s">
-        <v>163</v>
-      </c>
-      <c r="B56" s="19">
-        <v>39000</v>
-      </c>
-      <c r="C56" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="E56" s="18">
-        <v>400</v>
-      </c>
-      <c r="F56" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="H56" s="15">
-        <v>1980000</v>
-      </c>
-      <c r="I56" s="22" t="s">
-        <v>170</v>
-      </c>
-      <c r="K56" t="s">
+      <c r="L56" t="s">
+        <v>272</v>
+      </c>
+      <c r="M56" t="s">
         <v>171</v>
       </c>
-      <c r="M56" t="s">
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="57" spans="1:13">
-      <c r="A57" t="s">
-        <v>163</v>
-      </c>
       <c r="B57" s="19">
-        <v>81000</v>
+        <v>1000000</v>
       </c>
       <c r="C57" s="18" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E57" s="18">
-        <v>1600</v>
+        <v>300</v>
       </c>
       <c r="F57" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="H57" s="15">
-        <v>7910000</v>
+      <c r="H57" s="15" t="s">
+        <v>109</v>
       </c>
       <c r="I57" s="22" t="s">
-        <v>170</v>
+        <v>109</v>
       </c>
       <c r="K57" t="s">
-        <v>171</v>
+        <v>173</v>
+      </c>
+      <c r="L57" t="s">
+        <v>272</v>
       </c>
       <c r="M57" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>175</v>
+      </c>
+      <c r="B58" s="19">
+        <v>1000000</v>
+      </c>
+      <c r="C58" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="E58" s="18">
+        <v>500</v>
+      </c>
+      <c r="F58" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="H58" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="I58" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="K58" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="58" spans="1:13">
-      <c r="A58" t="s">
-        <v>174</v>
-      </c>
-      <c r="B58" s="19">
-        <v>1600000</v>
-      </c>
-      <c r="C58" s="18" t="s">
-        <v>175</v>
-      </c>
-      <c r="E58" s="18">
-        <v>77</v>
-      </c>
-      <c r="F58" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H58" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="I58" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="K58" t="s">
+      <c r="L58" t="s">
+        <v>272</v>
+      </c>
+      <c r="M58" t="s">
         <v>176</v>
       </c>
-      <c r="M58" t="s">
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>172</v>
+      </c>
+      <c r="B59" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="C59" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="E59" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="F59" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="H59" s="15">
+        <v>200000</v>
+      </c>
+      <c r="I59" s="22" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="59" spans="1:13">
-      <c r="A59" t="s">
-        <v>174</v>
-      </c>
-      <c r="B59" s="19">
-        <v>4900000</v>
-      </c>
-      <c r="C59" s="18" t="s">
-        <v>175</v>
-      </c>
-      <c r="E59" s="18">
-        <v>110</v>
-      </c>
-      <c r="F59" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H59" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="I59" s="22" t="s">
-        <v>111</v>
-      </c>
       <c r="K59" t="s">
-        <v>176</v>
+        <v>178</v>
+      </c>
+      <c r="L59" t="s">
+        <v>272</v>
       </c>
       <c r="M59" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>172</v>
+      </c>
+      <c r="B60" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="C60" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="E60" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="F60" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="H60" s="15">
+        <v>700000</v>
+      </c>
+      <c r="I60" s="22" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="60" spans="1:13">
-      <c r="A60" t="s">
-        <v>174</v>
-      </c>
-      <c r="B60" s="19">
-        <v>5000000</v>
-      </c>
-      <c r="C60" s="18" t="s">
-        <v>175</v>
-      </c>
-      <c r="E60" s="18">
-        <v>152</v>
-      </c>
-      <c r="F60" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H60" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="I60" s="22" t="s">
-        <v>111</v>
-      </c>
       <c r="K60" t="s">
-        <v>176</v>
+        <v>178</v>
+      </c>
+      <c r="L60" t="s">
+        <v>272</v>
       </c>
       <c r="M60" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>172</v>
+      </c>
+      <c r="B61" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="C61" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="E61" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="F61" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="H61" s="15">
+        <v>1200000</v>
+      </c>
+      <c r="I61" s="22" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="61" spans="1:13">
-      <c r="A61" t="s">
-        <v>174</v>
-      </c>
-      <c r="B61" s="19">
-        <v>10100000</v>
-      </c>
-      <c r="C61" s="18" t="s">
-        <v>175</v>
-      </c>
-      <c r="E61" s="18">
-        <v>178</v>
-      </c>
-      <c r="F61" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H61" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="I61" s="22" t="s">
-        <v>111</v>
-      </c>
       <c r="K61" t="s">
-        <v>176</v>
+        <v>72</v>
+      </c>
+      <c r="L61" t="s">
+        <v>272</v>
       </c>
       <c r="M61" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>172</v>
+      </c>
+      <c r="B62" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="C62" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="E62" s="18">
+        <v>1400</v>
+      </c>
+      <c r="F62" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="H62" s="15">
+        <v>6000000</v>
+      </c>
+      <c r="I62" s="22" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="62" spans="1:13">
-      <c r="A62" t="s">
-        <v>174</v>
-      </c>
-      <c r="B62" s="19">
-        <v>6100000</v>
-      </c>
-      <c r="C62" s="18" t="s">
-        <v>175</v>
-      </c>
-      <c r="E62" s="18">
-        <v>251</v>
-      </c>
-      <c r="F62" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H62" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="I62" s="22" t="s">
-        <v>111</v>
-      </c>
       <c r="K62" t="s">
-        <v>176</v>
+        <v>165</v>
+      </c>
+      <c r="L62" t="s">
+        <v>272</v>
       </c>
       <c r="M62" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>172</v>
+      </c>
+      <c r="B63" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="C63" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="E63" s="18">
+        <v>600</v>
+      </c>
+      <c r="F63" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="H63" s="15">
+        <v>3000000</v>
+      </c>
+      <c r="I63" s="22" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="63" spans="1:13">
-      <c r="A63" t="s">
-        <v>174</v>
-      </c>
-      <c r="B63" s="19">
-        <v>10100000</v>
-      </c>
-      <c r="C63" s="18" t="s">
-        <v>175</v>
-      </c>
-      <c r="E63" s="18">
-        <v>294</v>
-      </c>
-      <c r="F63" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H63" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="I63" s="22" t="s">
-        <v>111</v>
-      </c>
       <c r="K63" t="s">
-        <v>176</v>
+        <v>119</v>
+      </c>
+      <c r="L63" t="s">
+        <v>272</v>
       </c>
       <c r="M63" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="B64" s="19">
-        <v>7600000</v>
+        <v>1145000</v>
       </c>
       <c r="C64" s="18" t="s">
-        <v>175</v>
+        <v>153</v>
+      </c>
+      <c r="D64" s="20" t="s">
+        <v>185</v>
       </c>
       <c r="E64" s="18">
+        <v>250</v>
+      </c>
+      <c r="F64" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="H64" s="15">
+        <v>135</v>
+      </c>
+      <c r="I64" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="K64" t="s">
+        <v>72</v>
+      </c>
+      <c r="L64" t="s">
+        <v>272</v>
+      </c>
+      <c r="M64" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>184</v>
+      </c>
+      <c r="B65" s="19">
+        <v>1323500</v>
+      </c>
+      <c r="C65" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="D65" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="E65" s="18">
+        <v>500</v>
+      </c>
+      <c r="F65" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="H65" s="15">
+        <v>269</v>
+      </c>
+      <c r="I65" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="K65" t="s">
+        <v>72</v>
+      </c>
+      <c r="L65" t="s">
+        <v>272</v>
+      </c>
+      <c r="M65" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>184</v>
+      </c>
+      <c r="B66" s="19">
+        <v>1699000</v>
+      </c>
+      <c r="C66" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="D66" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="E66" s="18">
+        <v>1000</v>
+      </c>
+      <c r="F66" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="H66" s="15">
+        <v>539</v>
+      </c>
+      <c r="I66" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="K66" t="s">
+        <v>72</v>
+      </c>
+      <c r="L66" t="s">
+        <v>272</v>
+      </c>
+      <c r="M66" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>184</v>
+      </c>
+      <c r="B67" s="19">
+        <v>1407500</v>
+      </c>
+      <c r="C67" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="D67" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="E67" s="18">
+        <v>500</v>
+      </c>
+      <c r="F67" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="H67" s="15">
+        <v>264</v>
+      </c>
+      <c r="I67" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="K67" t="s">
+        <v>119</v>
+      </c>
+      <c r="L67" t="s">
+        <v>272</v>
+      </c>
+      <c r="M67" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>184</v>
+      </c>
+      <c r="B68" s="19">
+        <v>1840800</v>
+      </c>
+      <c r="C68" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="D68" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="E68" s="18">
+        <v>1000</v>
+      </c>
+      <c r="F68" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="H68" s="15">
+        <v>528</v>
+      </c>
+      <c r="I68" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="K68" t="s">
+        <v>119</v>
+      </c>
+      <c r="L68" t="s">
+        <v>272</v>
+      </c>
+      <c r="M68" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>184</v>
+      </c>
+      <c r="B69" s="19">
+        <v>2925000</v>
+      </c>
+      <c r="C69" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="D69" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="E69" s="18">
+        <v>2000</v>
+      </c>
+      <c r="F69" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="H69" s="15">
+        <v>1056</v>
+      </c>
+      <c r="I69" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="K69" t="s">
+        <v>119</v>
+      </c>
+      <c r="L69" t="s">
+        <v>272</v>
+      </c>
+      <c r="M69" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>184</v>
+      </c>
+      <c r="B70" s="19">
+        <v>996200</v>
+      </c>
+      <c r="C70" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="D70" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="E70" s="18">
+        <v>500</v>
+      </c>
+      <c r="F70" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="H70" s="15">
+        <v>272</v>
+      </c>
+      <c r="I70" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="K70" t="s">
+        <v>136</v>
+      </c>
+      <c r="L70" t="s">
+        <v>272</v>
+      </c>
+      <c r="M70" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>184</v>
+      </c>
+      <c r="B71" s="19">
+        <v>1068600</v>
+      </c>
+      <c r="C71" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="D71" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="E71" s="18">
+        <v>500</v>
+      </c>
+      <c r="F71" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="H71" s="15">
+        <v>264</v>
+      </c>
+      <c r="I71" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="K71" t="s">
+        <v>119</v>
+      </c>
+      <c r="L71" t="s">
+        <v>272</v>
+      </c>
+      <c r="M71" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>184</v>
+      </c>
+      <c r="B72" s="19">
+        <v>847400</v>
+      </c>
+      <c r="C72" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="D72" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="E72" s="18">
+        <v>250</v>
+      </c>
+      <c r="F72" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="H72" s="15">
+        <v>136</v>
+      </c>
+      <c r="I72" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="K72" t="s">
+        <v>136</v>
+      </c>
+      <c r="L72" t="s">
+        <v>272</v>
+      </c>
+      <c r="M72" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>184</v>
+      </c>
+      <c r="B73" s="19">
+        <v>1057400</v>
+      </c>
+      <c r="C73" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="D73" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="E73" s="18">
+        <v>500</v>
+      </c>
+      <c r="F73" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="H73" s="15">
+        <v>272</v>
+      </c>
+      <c r="I73" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="K73" t="s">
+        <v>136</v>
+      </c>
+      <c r="L73" t="s">
+        <v>272</v>
+      </c>
+      <c r="M73" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>184</v>
+      </c>
+      <c r="B74" s="19">
+        <v>1556100</v>
+      </c>
+      <c r="C74" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="D74" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="E74" s="18">
+        <v>1000</v>
+      </c>
+      <c r="F74" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="H74" s="15">
+        <v>544</v>
+      </c>
+      <c r="I74" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="K74" t="s">
+        <v>136</v>
+      </c>
+      <c r="L74" t="s">
+        <v>272</v>
+      </c>
+      <c r="M74" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>197</v>
+      </c>
+      <c r="B75" s="19">
+        <v>1977000</v>
+      </c>
+      <c r="C75" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E75" s="18">
+        <v>127</v>
+      </c>
+      <c r="F75" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="H75" s="15">
+        <v>70.099999999999994</v>
+      </c>
+      <c r="I75" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="K75" t="s">
+        <v>72</v>
+      </c>
+      <c r="L75" t="s">
+        <v>272</v>
+      </c>
+      <c r="M75" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>197</v>
+      </c>
+      <c r="B76" s="19">
+        <v>2030000</v>
+      </c>
+      <c r="C76" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E76" s="18">
         <v>300</v>
       </c>
-      <c r="F64" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H64" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="I64" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="K64" t="s">
-        <v>176</v>
-      </c>
-      <c r="M64" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="65" spans="1:14">
-      <c r="A65" t="s">
-        <v>174</v>
-      </c>
-      <c r="B65" s="19">
-        <v>7700000</v>
-      </c>
-      <c r="C65" s="18" t="s">
-        <v>175</v>
-      </c>
-      <c r="E65" s="18">
-        <v>349</v>
-      </c>
-      <c r="F65" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H65" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="I65" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="K65" t="s">
-        <v>176</v>
-      </c>
-      <c r="M65" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="66" spans="1:14">
-      <c r="A66" t="s">
-        <v>174</v>
-      </c>
-      <c r="B66" s="19">
-        <v>8200000</v>
-      </c>
-      <c r="C66" s="18" t="s">
-        <v>175</v>
-      </c>
-      <c r="E66" s="18">
-        <v>355</v>
-      </c>
-      <c r="F66" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H66" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="I66" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="K66" t="s">
-        <v>176</v>
-      </c>
-      <c r="M66" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="67" spans="1:14">
-      <c r="A67" t="s">
-        <v>174</v>
-      </c>
-      <c r="B67" s="19">
-        <v>9000000</v>
-      </c>
-      <c r="C67" s="18" t="s">
-        <v>175</v>
-      </c>
-      <c r="E67" s="18">
-        <v>498</v>
-      </c>
-      <c r="F67" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H67" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="I67" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="K67" t="s">
-        <v>176</v>
-      </c>
-      <c r="M67" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="68" spans="1:14">
-      <c r="A68" t="s">
-        <v>174</v>
-      </c>
-      <c r="B68" s="19">
-        <v>12000000</v>
-      </c>
-      <c r="C68" s="18" t="s">
-        <v>175</v>
-      </c>
-      <c r="E68" s="18">
-        <v>596</v>
-      </c>
-      <c r="F68" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H68" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="I68" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="K68" t="s">
-        <v>176</v>
-      </c>
-      <c r="M68" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="69" spans="1:14">
-      <c r="A69" t="s">
-        <v>174</v>
-      </c>
-      <c r="B69" s="19">
-        <v>13000000</v>
-      </c>
-      <c r="C69" s="18" t="s">
-        <v>175</v>
-      </c>
-      <c r="E69" s="18">
-        <v>596</v>
-      </c>
-      <c r="F69" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H69" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="I69" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="K69" t="s">
-        <v>176</v>
-      </c>
-      <c r="M69" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="70" spans="1:14">
-      <c r="A70" t="s">
-        <v>174</v>
-      </c>
-      <c r="B70" s="19">
-        <v>11000000</v>
-      </c>
-      <c r="C70" s="18" t="s">
-        <v>175</v>
-      </c>
-      <c r="E70" s="18">
-        <v>602</v>
-      </c>
-      <c r="F70" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H70" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="I70" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="K70" t="s">
-        <v>176</v>
-      </c>
-      <c r="M70" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="71" spans="1:14">
-      <c r="A71" t="s">
-        <v>174</v>
-      </c>
-      <c r="B71" s="19">
-        <v>22100000</v>
-      </c>
-      <c r="C71" s="18" t="s">
-        <v>175</v>
-      </c>
-      <c r="E71" s="18">
-        <v>1396</v>
-      </c>
-      <c r="F71" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H71" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="I71" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="K71" t="s">
-        <v>176</v>
-      </c>
-      <c r="M71" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="72" spans="1:14">
-      <c r="A72" t="s">
-        <v>174</v>
-      </c>
-      <c r="B72" s="19">
-        <v>23200000</v>
-      </c>
-      <c r="C72" s="18" t="s">
-        <v>175</v>
-      </c>
-      <c r="E72" s="18">
-        <v>1593</v>
-      </c>
-      <c r="F72" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H72" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="I72" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="K72" t="s">
-        <v>176</v>
-      </c>
-      <c r="M72" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="73" spans="1:14">
-      <c r="A73" t="s">
-        <v>174</v>
-      </c>
-      <c r="B73" s="19">
-        <v>1000000</v>
-      </c>
-      <c r="C73" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="E73" s="18">
-        <v>300</v>
-      </c>
-      <c r="F73" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H73" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="I73" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="K73" t="s">
-        <v>176</v>
-      </c>
-      <c r="M73" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="74" spans="1:14">
-      <c r="A74" t="s">
-        <v>180</v>
-      </c>
-      <c r="B74" s="19">
-        <v>1000000</v>
-      </c>
-      <c r="C74" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="E74" s="18">
-        <v>500</v>
-      </c>
-      <c r="F74" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H74" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="I74" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="K74" t="s">
-        <v>176</v>
-      </c>
-      <c r="M74" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="75" spans="1:14">
-      <c r="A75" t="s">
-        <v>174</v>
-      </c>
-      <c r="B75" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="C75" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="E75" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="F75" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="H75" s="15">
-        <v>200000</v>
-      </c>
-      <c r="I75" s="22" t="s">
-        <v>182</v>
-      </c>
-      <c r="K75" t="s">
-        <v>183</v>
-      </c>
-      <c r="M75" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="76" spans="1:14">
-      <c r="A76" t="s">
-        <v>174</v>
-      </c>
-      <c r="B76" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="C76" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="E76" s="18" t="s">
-        <v>111</v>
-      </c>
       <c r="F76" s="18" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="H76" s="15">
-        <v>700000</v>
+        <v>166</v>
       </c>
       <c r="I76" s="22" t="s">
-        <v>182</v>
+        <v>108</v>
       </c>
       <c r="K76" t="s">
-        <v>183</v>
+        <v>72</v>
+      </c>
+      <c r="L76" t="s">
+        <v>272</v>
       </c>
       <c r="M76" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="77" spans="1:14">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>174</v>
-      </c>
-      <c r="B77" s="19" t="s">
-        <v>111</v>
+        <v>197</v>
+      </c>
+      <c r="B77" s="19">
+        <v>2896000</v>
       </c>
       <c r="C77" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="E77" s="18" t="s">
-        <v>111</v>
+        <v>37</v>
+      </c>
+      <c r="E77" s="18">
+        <v>450</v>
       </c>
       <c r="F77" s="18" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="H77" s="15">
-        <v>1200000</v>
+        <v>252</v>
       </c>
       <c r="I77" s="22" t="s">
-        <v>182</v>
+        <v>108</v>
       </c>
       <c r="K77" t="s">
         <v>72</v>
       </c>
+      <c r="L77" t="s">
+        <v>272</v>
+      </c>
       <c r="M77" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="78" spans="1:14">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>174</v>
-      </c>
-      <c r="B78" s="19" t="s">
-        <v>111</v>
+        <v>197</v>
+      </c>
+      <c r="B78" s="19">
+        <v>3713000</v>
       </c>
       <c r="C78" s="18" t="s">
-        <v>111</v>
+        <v>37</v>
       </c>
       <c r="E78" s="18">
-        <v>1400</v>
+        <v>700</v>
       </c>
       <c r="F78" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H78" s="15">
-        <v>6000000</v>
+        <v>385</v>
       </c>
       <c r="I78" s="22" t="s">
-        <v>182</v>
+        <v>108</v>
       </c>
       <c r="K78" t="s">
-        <v>167</v>
+        <v>72</v>
+      </c>
+      <c r="L78" t="s">
+        <v>272</v>
       </c>
       <c r="M78" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="79" spans="1:14">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>174</v>
-      </c>
-      <c r="B79" s="19" t="s">
-        <v>111</v>
+        <v>197</v>
+      </c>
+      <c r="B79" s="19">
+        <v>4163000</v>
       </c>
       <c r="C79" s="18" t="s">
-        <v>111</v>
+        <v>37</v>
       </c>
       <c r="E79" s="18">
+        <v>900</v>
+      </c>
+      <c r="F79" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="H79" s="15">
+        <v>496</v>
+      </c>
+      <c r="I79" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="K79" t="s">
+        <v>72</v>
+      </c>
+      <c r="L79" t="s">
+        <v>272</v>
+      </c>
+      <c r="M79" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>197</v>
+      </c>
+      <c r="B80" s="19">
+        <v>4405000</v>
+      </c>
+      <c r="C80" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E80" s="18">
+        <v>475</v>
+      </c>
+      <c r="F80" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="H80" s="15">
+        <v>256</v>
+      </c>
+      <c r="I80" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="K80" t="s">
+        <v>203</v>
+      </c>
+      <c r="L80" t="s">
+        <v>272</v>
+      </c>
+      <c r="M80" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>197</v>
+      </c>
+      <c r="B81" s="19">
+        <v>6773000</v>
+      </c>
+      <c r="C81" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E81" s="18">
+        <v>1110</v>
+      </c>
+      <c r="F81" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="H81" s="15">
+        <v>599</v>
+      </c>
+      <c r="I81" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="K81" t="s">
+        <v>203</v>
+      </c>
+      <c r="L81" t="s">
+        <v>272</v>
+      </c>
+      <c r="M81" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>197</v>
+      </c>
+      <c r="B82" s="19">
+        <v>10263000</v>
+      </c>
+      <c r="C82" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E82" s="18">
+        <v>3960</v>
+      </c>
+      <c r="F82" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="H82" s="15">
+        <v>1996</v>
+      </c>
+      <c r="I82" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="K82" t="s">
+        <v>206</v>
+      </c>
+      <c r="L82" t="s">
+        <v>272</v>
+      </c>
+      <c r="M82" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>208</v>
+      </c>
+      <c r="B83" s="19">
+        <v>5500</v>
+      </c>
+      <c r="C83" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="E83" s="18">
+        <v>100</v>
+      </c>
+      <c r="F83" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="H83" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="I83" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="K83" t="s">
+        <v>72</v>
+      </c>
+      <c r="L83" t="s">
+        <v>272</v>
+      </c>
+      <c r="M83" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>208</v>
+      </c>
+      <c r="B84" s="19">
+        <v>2500</v>
+      </c>
+      <c r="C84" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="E84" s="18">
+        <v>500</v>
+      </c>
+      <c r="F84" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="H84" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="I84" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="K84" t="s">
+        <v>72</v>
+      </c>
+      <c r="L84" t="s">
+        <v>272</v>
+      </c>
+      <c r="M84" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>208</v>
+      </c>
+      <c r="B85" s="19">
+        <v>1800</v>
+      </c>
+      <c r="C85" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="E85" s="18">
+        <v>1000</v>
+      </c>
+      <c r="F85" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="H85" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="I85" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="K85" t="s">
+        <v>72</v>
+      </c>
+      <c r="L85" t="s">
+        <v>272</v>
+      </c>
+      <c r="M85" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>208</v>
+      </c>
+      <c r="B86" s="19">
+        <v>2000</v>
+      </c>
+      <c r="C86" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="E86" s="18">
+        <v>1000</v>
+      </c>
+      <c r="F86" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="H86" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="I86" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="K86" t="s">
+        <v>72</v>
+      </c>
+      <c r="L86" t="s">
+        <v>272</v>
+      </c>
+      <c r="M86" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>208</v>
+      </c>
+      <c r="B87" s="19">
+        <v>4500</v>
+      </c>
+      <c r="C87" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="E87" s="18">
+        <v>250</v>
+      </c>
+      <c r="F87" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="H87" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="I87" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="K87" t="s">
+        <v>144</v>
+      </c>
+      <c r="L87" t="s">
+        <v>272</v>
+      </c>
+      <c r="M87" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>208</v>
+      </c>
+      <c r="B88" s="19">
+        <v>2000</v>
+      </c>
+      <c r="C88" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="E88" s="18">
+        <v>1000</v>
+      </c>
+      <c r="F88" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="H88" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="I88" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="K88" t="s">
+        <v>144</v>
+      </c>
+      <c r="L88" t="s">
+        <v>272</v>
+      </c>
+      <c r="M88" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>208</v>
+      </c>
+      <c r="B89" s="19">
+        <v>1500</v>
+      </c>
+      <c r="C89" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="E89" s="18">
+        <v>1500</v>
+      </c>
+      <c r="F89" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="H89" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="I89" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="K89" t="s">
+        <v>144</v>
+      </c>
+      <c r="L89" t="s">
+        <v>272</v>
+      </c>
+      <c r="M89" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>208</v>
+      </c>
+      <c r="B90" s="19">
+        <v>3200</v>
+      </c>
+      <c r="C90" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="E90" s="18">
         <v>600</v>
       </c>
-      <c r="F79" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H79" s="15">
-        <v>3000000</v>
-      </c>
-      <c r="I79" s="22" t="s">
-        <v>182</v>
-      </c>
-      <c r="K79" t="s">
-        <v>121</v>
-      </c>
-      <c r="M79" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="80" spans="1:14">
-      <c r="A80" t="s">
-        <v>189</v>
-      </c>
-      <c r="B80" s="19">
-        <v>1145000</v>
-      </c>
-      <c r="C80" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="D80" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="E80" s="18">
-        <v>250</v>
-      </c>
-      <c r="F80" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H80" s="15">
-        <v>135</v>
-      </c>
-      <c r="I80" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="K80" t="s">
+      <c r="F90" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="H90" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="I90" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="K90" t="s">
+        <v>136</v>
+      </c>
+      <c r="L90" t="s">
+        <v>272</v>
+      </c>
+      <c r="M90" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>208</v>
+      </c>
+      <c r="B91" s="19">
+        <v>1500</v>
+      </c>
+      <c r="C91" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="E91" s="18">
+        <v>1800</v>
+      </c>
+      <c r="F91" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="H91" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="I91" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="K91" t="s">
+        <v>136</v>
+      </c>
+      <c r="L91" t="s">
+        <v>272</v>
+      </c>
+      <c r="M91" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>208</v>
+      </c>
+      <c r="B92" s="19">
+        <v>2700</v>
+      </c>
+      <c r="C92" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="E92" s="18">
+        <v>600</v>
+      </c>
+      <c r="F92" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="H92" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="I92" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="K92" t="s">
+        <v>119</v>
+      </c>
+      <c r="L92" t="s">
+        <v>272</v>
+      </c>
+      <c r="M92" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>208</v>
+      </c>
+      <c r="B93" s="19">
+        <v>1500</v>
+      </c>
+      <c r="C93" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="E93" s="18">
+        <v>2000</v>
+      </c>
+      <c r="F93" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="H93" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="I93" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="K93" t="s">
+        <v>119</v>
+      </c>
+      <c r="L93" t="s">
+        <v>272</v>
+      </c>
+      <c r="M93" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>208</v>
+      </c>
+      <c r="B94" s="19">
+        <v>6000</v>
+      </c>
+      <c r="C94" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="E94" s="18">
+        <v>100</v>
+      </c>
+      <c r="F94" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="H94" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="I94" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="K94" t="s">
+        <v>127</v>
+      </c>
+      <c r="L94" t="s">
+        <v>272</v>
+      </c>
+      <c r="M94" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>208</v>
+      </c>
+      <c r="B95" s="19">
+        <v>2500</v>
+      </c>
+      <c r="C95" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="E95" s="18">
+        <v>400</v>
+      </c>
+      <c r="F95" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="H95" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="I95" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="K95" t="s">
+        <v>127</v>
+      </c>
+      <c r="L95" t="s">
+        <v>272</v>
+      </c>
+      <c r="M95" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>208</v>
+      </c>
+      <c r="B96" s="19">
+        <v>2000</v>
+      </c>
+      <c r="C96" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="E96" s="18">
+        <v>1000</v>
+      </c>
+      <c r="F96" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="H96" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="I96" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="K96" t="s">
+        <v>127</v>
+      </c>
+      <c r="L96" t="s">
+        <v>272</v>
+      </c>
+      <c r="M96" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>223</v>
+      </c>
+      <c r="B97" s="19">
+        <v>5500</v>
+      </c>
+      <c r="C97" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="E97" s="18">
+        <v>100</v>
+      </c>
+      <c r="F97" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="H97" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="I97" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="K97" t="s">
         <v>72</v>
       </c>
-      <c r="L80" t="s">
-        <v>191</v>
-      </c>
-      <c r="N80" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="81" spans="1:14">
-      <c r="A81" t="s">
-        <v>189</v>
-      </c>
-      <c r="B81" s="19">
-        <v>1323500</v>
-      </c>
-      <c r="C81" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="D81" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="E81" s="18">
+      <c r="L97" t="s">
+        <v>272</v>
+      </c>
+      <c r="M97" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>223</v>
+      </c>
+      <c r="B98" s="19">
+        <v>2500</v>
+      </c>
+      <c r="C98" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="E98" s="18">
         <v>500</v>
       </c>
-      <c r="F81" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H81" s="15">
-        <v>269</v>
-      </c>
-      <c r="I81" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="K81" t="s">
+      <c r="F98" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="H98" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="I98" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="K98" t="s">
         <v>72</v>
       </c>
-      <c r="L81" t="s">
-        <v>191</v>
-      </c>
-      <c r="N81" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="82" spans="1:14">
-      <c r="A82" t="s">
-        <v>189</v>
-      </c>
-      <c r="B82" s="19">
-        <v>1699000</v>
-      </c>
-      <c r="C82" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="D82" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="E82" s="18">
+      <c r="L98" t="s">
+        <v>272</v>
+      </c>
+      <c r="M98" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>223</v>
+      </c>
+      <c r="B99" s="19">
+        <v>1800</v>
+      </c>
+      <c r="C99" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="E99" s="18">
         <v>1000</v>
       </c>
-      <c r="F82" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H82" s="15">
-        <v>539</v>
-      </c>
-      <c r="I82" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="K82" t="s">
-        <v>72</v>
-      </c>
-      <c r="L82" t="s">
-        <v>191</v>
-      </c>
-      <c r="N82" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="83" spans="1:14">
-      <c r="A83" t="s">
-        <v>189</v>
-      </c>
-      <c r="B83" s="19">
-        <v>1407500</v>
-      </c>
-      <c r="C83" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="D83" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="E83" s="18">
-        <v>500</v>
-      </c>
-      <c r="F83" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H83" s="15">
-        <v>264</v>
-      </c>
-      <c r="I83" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="K83" t="s">
-        <v>121</v>
-      </c>
-      <c r="L83" t="s">
-        <v>191</v>
-      </c>
-      <c r="N83" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="84" spans="1:14">
-      <c r="A84" t="s">
-        <v>189</v>
-      </c>
-      <c r="B84" s="19">
-        <v>1840800</v>
-      </c>
-      <c r="C84" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="D84" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="E84" s="18">
-        <v>1000</v>
-      </c>
-      <c r="F84" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H84" s="15">
-        <v>528</v>
-      </c>
-      <c r="I84" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="K84" t="s">
-        <v>121</v>
-      </c>
-      <c r="L84" t="s">
-        <v>191</v>
-      </c>
-      <c r="N84" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="85" spans="1:14">
-      <c r="A85" t="s">
-        <v>189</v>
-      </c>
-      <c r="B85" s="19">
-        <v>2925000</v>
-      </c>
-      <c r="C85" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="D85" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="E85" s="18">
-        <v>2000</v>
-      </c>
-      <c r="F85" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H85" s="15">
-        <v>1056</v>
-      </c>
-      <c r="I85" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="K85" t="s">
-        <v>121</v>
-      </c>
-      <c r="L85" t="s">
-        <v>191</v>
-      </c>
-      <c r="N85" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="86" spans="1:14">
-      <c r="A86" t="s">
-        <v>189</v>
-      </c>
-      <c r="B86" s="19">
-        <v>996200</v>
-      </c>
-      <c r="C86" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="D86" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="E86" s="18">
-        <v>500</v>
-      </c>
-      <c r="F86" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H86" s="15">
-        <v>272</v>
-      </c>
-      <c r="I86" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="K86" t="s">
-        <v>138</v>
-      </c>
-      <c r="L86" t="s">
-        <v>191</v>
-      </c>
-      <c r="N86" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="87" spans="1:14">
-      <c r="A87" t="s">
-        <v>189</v>
-      </c>
-      <c r="B87" s="19">
-        <v>1068600</v>
-      </c>
-      <c r="C87" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="D87" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="E87" s="18">
-        <v>500</v>
-      </c>
-      <c r="F87" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H87" s="15">
-        <v>264</v>
-      </c>
-      <c r="I87" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="K87" t="s">
-        <v>121</v>
-      </c>
-      <c r="L87" t="s">
-        <v>191</v>
-      </c>
-      <c r="N87" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="88" spans="1:14">
-      <c r="A88" t="s">
-        <v>189</v>
-      </c>
-      <c r="B88" s="19">
-        <v>847400</v>
-      </c>
-      <c r="C88" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="D88" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="E88" s="18">
-        <v>250</v>
-      </c>
-      <c r="F88" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H88" s="15">
-        <v>136</v>
-      </c>
-      <c r="I88" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="K88" t="s">
-        <v>138</v>
-      </c>
-      <c r="L88" t="s">
-        <v>191</v>
-      </c>
-      <c r="N88" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="89" spans="1:14">
-      <c r="A89" t="s">
-        <v>189</v>
-      </c>
-      <c r="B89" s="19">
-        <v>1057400</v>
-      </c>
-      <c r="C89" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="D89" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="E89" s="18">
-        <v>500</v>
-      </c>
-      <c r="F89" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H89" s="15">
-        <v>272</v>
-      </c>
-      <c r="I89" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="K89" t="s">
-        <v>138</v>
-      </c>
-      <c r="L89" t="s">
-        <v>191</v>
-      </c>
-      <c r="N89" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="90" spans="1:14">
-      <c r="A90" t="s">
-        <v>189</v>
-      </c>
-      <c r="B90" s="19">
-        <v>1556100</v>
-      </c>
-      <c r="C90" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="D90" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="E90" s="18">
-        <v>1000</v>
-      </c>
-      <c r="F90" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H90" s="15">
-        <v>544</v>
-      </c>
-      <c r="I90" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="K90" t="s">
-        <v>138</v>
-      </c>
-      <c r="L90" t="s">
-        <v>191</v>
-      </c>
-      <c r="N90" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="91" spans="1:14">
-      <c r="A91" t="s">
-        <v>203</v>
-      </c>
-      <c r="B91" s="19">
-        <v>1977000</v>
-      </c>
-      <c r="C91" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="E91" s="18">
-        <v>127</v>
-      </c>
-      <c r="F91" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H91" s="15">
-        <v>70.099999999999994</v>
-      </c>
-      <c r="I91" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="K91" t="s">
-        <v>72</v>
-      </c>
-      <c r="M91" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="92" spans="1:14">
-      <c r="A92" t="s">
-        <v>203</v>
-      </c>
-      <c r="B92" s="19">
-        <v>2030000</v>
-      </c>
-      <c r="C92" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="E92" s="18">
-        <v>300</v>
-      </c>
-      <c r="F92" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H92" s="15">
-        <v>166</v>
-      </c>
-      <c r="I92" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="K92" t="s">
-        <v>72</v>
-      </c>
-      <c r="L92" t="s">
-        <v>191</v>
-      </c>
-      <c r="N92" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="93" spans="1:14">
-      <c r="A93" t="s">
-        <v>203</v>
-      </c>
-      <c r="B93" s="19">
-        <v>2896000</v>
-      </c>
-      <c r="C93" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="E93" s="18">
-        <v>450</v>
-      </c>
-      <c r="F93" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H93" s="15">
-        <v>252</v>
-      </c>
-      <c r="I93" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="K93" t="s">
-        <v>72</v>
-      </c>
-      <c r="L93" t="s">
-        <v>191</v>
-      </c>
-      <c r="N93" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="94" spans="1:14">
-      <c r="A94" t="s">
-        <v>203</v>
-      </c>
-      <c r="B94" s="19">
-        <v>3713000</v>
-      </c>
-      <c r="C94" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="E94" s="18">
-        <v>700</v>
-      </c>
-      <c r="F94" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H94" s="15">
-        <v>385</v>
-      </c>
-      <c r="I94" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="K94" t="s">
-        <v>72</v>
-      </c>
-      <c r="L94" t="s">
-        <v>191</v>
-      </c>
-      <c r="N94" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="95" spans="1:14">
-      <c r="A95" t="s">
-        <v>203</v>
-      </c>
-      <c r="B95" s="19">
-        <v>4163000</v>
-      </c>
-      <c r="C95" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="E95" s="18">
-        <v>900</v>
-      </c>
-      <c r="F95" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H95" s="15">
-        <v>496</v>
-      </c>
-      <c r="I95" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="K95" t="s">
-        <v>72</v>
-      </c>
-      <c r="L95" t="s">
-        <v>191</v>
-      </c>
-      <c r="N95" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="96" spans="1:14">
-      <c r="A96" t="s">
-        <v>203</v>
-      </c>
-      <c r="B96" s="19">
-        <v>4405000</v>
-      </c>
-      <c r="C96" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="E96" s="18">
-        <v>475</v>
-      </c>
-      <c r="F96" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H96" s="15">
-        <v>256</v>
-      </c>
-      <c r="I96" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="K96" t="s">
-        <v>209</v>
-      </c>
-      <c r="L96" t="s">
-        <v>191</v>
-      </c>
-      <c r="N96" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="97" spans="1:14">
-      <c r="A97" t="s">
-        <v>203</v>
-      </c>
-      <c r="B97" s="19">
-        <v>6773000</v>
-      </c>
-      <c r="C97" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="E97" s="18">
-        <v>1110</v>
-      </c>
-      <c r="F97" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H97" s="15">
-        <v>599</v>
-      </c>
-      <c r="I97" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="K97" t="s">
-        <v>209</v>
-      </c>
-      <c r="L97" t="s">
-        <v>191</v>
-      </c>
-      <c r="N97" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="98" spans="1:14">
-      <c r="A98" t="s">
-        <v>203</v>
-      </c>
-      <c r="B98" s="19">
-        <v>10263000</v>
-      </c>
-      <c r="C98" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="E98" s="18">
-        <v>3960</v>
-      </c>
-      <c r="F98" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H98" s="15">
-        <v>1996</v>
-      </c>
-      <c r="I98" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="K98" t="s">
-        <v>212</v>
-      </c>
-      <c r="L98" t="s">
-        <v>191</v>
-      </c>
-      <c r="N98" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="99" spans="1:14">
-      <c r="A99" t="s">
-        <v>214</v>
-      </c>
-      <c r="B99" s="19">
-        <v>5500</v>
-      </c>
-      <c r="C99" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="E99" s="18">
-        <v>100</v>
-      </c>
       <c r="F99" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H99" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I99" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K99" t="s">
         <v>72</v>
       </c>
       <c r="L99" t="s">
-        <v>191</v>
-      </c>
-      <c r="N99" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="100" spans="1:14">
+        <v>272</v>
+      </c>
+      <c r="M99" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="B100" s="19">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="C100" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E100" s="18">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="F100" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H100" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I100" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K100" t="s">
         <v>72</v>
       </c>
       <c r="L100" t="s">
-        <v>191</v>
-      </c>
-      <c r="N100" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="101" spans="1:14">
+        <v>272</v>
+      </c>
+      <c r="M100" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="B101" s="19">
-        <v>1800</v>
+        <v>4500</v>
       </c>
       <c r="C101" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E101" s="18">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="F101" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H101" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I101" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K101" t="s">
-        <v>72</v>
+        <v>144</v>
       </c>
       <c r="L101" t="s">
-        <v>191</v>
-      </c>
-      <c r="N101" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="102" spans="1:14">
+        <v>272</v>
+      </c>
+      <c r="M101" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="B102" s="19">
         <v>2000</v>
       </c>
       <c r="C102" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E102" s="18">
         <v>1000</v>
       </c>
       <c r="F102" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H102" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I102" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K102" t="s">
-        <v>72</v>
+        <v>144</v>
       </c>
       <c r="L102" t="s">
-        <v>191</v>
-      </c>
-      <c r="N102" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="103" spans="1:14">
+        <v>272</v>
+      </c>
+      <c r="M102" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="B103" s="19">
-        <v>4500</v>
+        <v>1500</v>
       </c>
       <c r="C103" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E103" s="18">
-        <v>250</v>
+        <v>1500</v>
       </c>
       <c r="F103" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H103" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I103" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K103" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L103" t="s">
-        <v>191</v>
-      </c>
-      <c r="N103" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="104" spans="1:14">
+        <v>272</v>
+      </c>
+      <c r="M103" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="B104" s="19">
-        <v>2000</v>
+        <v>3200</v>
       </c>
       <c r="C104" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E104" s="18">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="F104" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H104" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I104" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K104" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="L104" t="s">
-        <v>191</v>
-      </c>
-      <c r="N104" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="105" spans="1:14">
+        <v>272</v>
+      </c>
+      <c r="M104" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="B105" s="19">
         <v>1500</v>
       </c>
       <c r="C105" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E105" s="18">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="F105" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H105" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I105" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K105" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="L105" t="s">
-        <v>191</v>
-      </c>
-      <c r="N105" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="106" spans="1:14">
+        <v>272</v>
+      </c>
+      <c r="M105" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="B106" s="19">
-        <v>3200</v>
+        <v>2700</v>
       </c>
       <c r="C106" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E106" s="18">
         <v>600</v>
       </c>
       <c r="F106" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H106" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I106" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K106" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="L106" t="s">
-        <v>191</v>
-      </c>
-      <c r="N106" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="107" spans="1:14">
+        <v>272</v>
+      </c>
+      <c r="M106" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="B107" s="19">
         <v>1500</v>
       </c>
       <c r="C107" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E107" s="18">
-        <v>1800</v>
+        <v>2000</v>
       </c>
       <c r="F107" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H107" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I107" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K107" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="L107" t="s">
-        <v>191</v>
-      </c>
-      <c r="N107" t="s">
+        <v>272</v>
+      </c>
+      <c r="M107" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="108" spans="1:14">
-      <c r="A108" t="s">
-        <v>214</v>
-      </c>
       <c r="B108" s="19">
-        <v>2700</v>
+        <v>2500</v>
       </c>
       <c r="C108" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E108" s="18">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="F108" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H108" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I108" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K108" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="L108" t="s">
-        <v>191</v>
-      </c>
-      <c r="N108" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="109" spans="1:14">
+        <v>272</v>
+      </c>
+      <c r="M108" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="B109" s="19">
-        <v>1500</v>
+        <v>6000</v>
       </c>
       <c r="C109" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E109" s="18">
+        <v>400</v>
+      </c>
+      <c r="F109" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="H109" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="I109" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="K109" t="s">
+        <v>127</v>
+      </c>
+      <c r="L109" t="s">
+        <v>272</v>
+      </c>
+      <c r="M109" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>223</v>
+      </c>
+      <c r="B110" s="19">
         <v>2000</v>
       </c>
-      <c r="F109" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H109" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="I109" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="K109" t="s">
-        <v>121</v>
-      </c>
-      <c r="L109" t="s">
-        <v>191</v>
-      </c>
-      <c r="N109" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="110" spans="1:14">
-      <c r="A110" t="s">
-        <v>214</v>
-      </c>
-      <c r="B110" s="19">
-        <v>6000</v>
-      </c>
       <c r="C110" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E110" s="18">
+        <v>1000</v>
+      </c>
+      <c r="F110" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="H110" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="I110" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="K110" t="s">
+        <v>127</v>
+      </c>
+      <c r="L110" t="s">
+        <v>272</v>
+      </c>
+      <c r="M110" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>238</v>
+      </c>
+      <c r="B111" s="19">
+        <v>1163849</v>
+      </c>
+      <c r="C111" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E111" s="18">
+        <v>1000</v>
+      </c>
+      <c r="F111" s="18" t="s">
+        <v>239</v>
+      </c>
+      <c r="H111" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="I111" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="K111" t="s">
+        <v>240</v>
+      </c>
+      <c r="L111" t="s">
+        <v>272</v>
+      </c>
+      <c r="M111" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>242</v>
+      </c>
+      <c r="B112" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="C112" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="E112" s="18">
+        <v>180</v>
+      </c>
+      <c r="F112" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="H112" s="15">
         <v>100</v>
       </c>
-      <c r="F110" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H110" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="I110" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="K110" t="s">
-        <v>129</v>
-      </c>
-      <c r="L110" t="s">
-        <v>191</v>
-      </c>
-      <c r="N110" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="111" spans="1:14">
-      <c r="A111" t="s">
-        <v>214</v>
-      </c>
-      <c r="B111" s="19">
-        <v>2500</v>
-      </c>
-      <c r="C111" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="E111" s="18">
-        <v>400</v>
-      </c>
-      <c r="F111" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H111" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="I111" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="K111" t="s">
-        <v>129</v>
-      </c>
-      <c r="L111" t="s">
-        <v>191</v>
-      </c>
-      <c r="N111" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="112" spans="1:14">
-      <c r="A112" t="s">
-        <v>214</v>
-      </c>
-      <c r="B112" s="19">
-        <v>2000</v>
-      </c>
-      <c r="C112" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="E112" s="18">
-        <v>1000</v>
-      </c>
-      <c r="F112" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H112" s="15" t="s">
-        <v>111</v>
-      </c>
       <c r="I112" s="22" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="K112" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="L112" t="s">
-        <v>191</v>
-      </c>
-      <c r="N112" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="113" spans="1:14">
-      <c r="A113" t="s">
-        <v>229</v>
-      </c>
-      <c r="B113" s="19">
-        <v>5500</v>
-      </c>
-      <c r="C113" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="E113" s="18">
-        <v>100</v>
-      </c>
-      <c r="F113" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H113" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="I113" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="K113" t="s">
-        <v>72</v>
-      </c>
-      <c r="L113" t="s">
-        <v>191</v>
-      </c>
-      <c r="N113" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="114" spans="1:14">
-      <c r="A114" t="s">
-        <v>229</v>
-      </c>
-      <c r="B114" s="19">
-        <v>2500</v>
-      </c>
-      <c r="C114" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="E114" s="18">
-        <v>500</v>
-      </c>
-      <c r="F114" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H114" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="I114" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="K114" t="s">
-        <v>72</v>
-      </c>
-      <c r="L114" t="s">
-        <v>191</v>
-      </c>
-      <c r="N114" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="115" spans="1:14">
-      <c r="A115" t="s">
-        <v>229</v>
-      </c>
-      <c r="B115" s="19">
-        <v>1800</v>
-      </c>
-      <c r="C115" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="E115" s="18">
-        <v>1000</v>
-      </c>
-      <c r="F115" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H115" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="I115" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="K115" t="s">
-        <v>72</v>
-      </c>
-      <c r="L115" t="s">
-        <v>191</v>
-      </c>
-      <c r="N115" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="116" spans="1:14">
-      <c r="A116" t="s">
-        <v>229</v>
-      </c>
-      <c r="B116" s="19">
-        <v>2000</v>
-      </c>
-      <c r="C116" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="E116" s="18">
-        <v>1000</v>
-      </c>
-      <c r="F116" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H116" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="I116" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="K116" t="s">
-        <v>72</v>
-      </c>
-      <c r="L116" t="s">
-        <v>191</v>
-      </c>
-      <c r="N116" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="117" spans="1:14">
-      <c r="A117" t="s">
-        <v>229</v>
-      </c>
-      <c r="B117" s="19">
-        <v>4500</v>
-      </c>
-      <c r="C117" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="E117" s="18">
-        <v>250</v>
-      </c>
-      <c r="F117" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H117" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="I117" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="K117" t="s">
-        <v>146</v>
-      </c>
-      <c r="L117" t="s">
-        <v>191</v>
-      </c>
-      <c r="N117" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="118" spans="1:14">
-      <c r="A118" t="s">
-        <v>229</v>
-      </c>
-      <c r="B118" s="19">
-        <v>2000</v>
-      </c>
-      <c r="C118" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="E118" s="18">
-        <v>1000</v>
-      </c>
-      <c r="F118" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H118" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="I118" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="K118" t="s">
-        <v>146</v>
-      </c>
-      <c r="L118" t="s">
-        <v>191</v>
-      </c>
-      <c r="N118" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="119" spans="1:14">
-      <c r="A119" t="s">
-        <v>229</v>
-      </c>
-      <c r="B119" s="19">
-        <v>1500</v>
-      </c>
-      <c r="C119" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="E119" s="18">
-        <v>1500</v>
-      </c>
-      <c r="F119" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H119" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="I119" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="K119" t="s">
-        <v>146</v>
-      </c>
-      <c r="L119" t="s">
-        <v>191</v>
-      </c>
-      <c r="N119" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="120" spans="1:14">
-      <c r="A120" t="s">
-        <v>229</v>
-      </c>
-      <c r="B120" s="19">
-        <v>3200</v>
-      </c>
-      <c r="C120" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="E120" s="18">
-        <v>600</v>
-      </c>
-      <c r="F120" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H120" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="I120" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="K120" t="s">
-        <v>138</v>
-      </c>
-      <c r="L120" t="s">
-        <v>191</v>
-      </c>
-      <c r="N120" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="121" spans="1:14">
-      <c r="A121" t="s">
-        <v>229</v>
-      </c>
-      <c r="B121" s="19">
-        <v>1500</v>
-      </c>
-      <c r="C121" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="E121" s="18">
-        <v>1800</v>
-      </c>
-      <c r="F121" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H121" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="I121" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="K121" t="s">
-        <v>138</v>
-      </c>
-      <c r="L121" t="s">
-        <v>191</v>
-      </c>
-      <c r="N121" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="122" spans="1:14">
-      <c r="A122" t="s">
-        <v>229</v>
-      </c>
-      <c r="B122" s="19">
-        <v>2700</v>
-      </c>
-      <c r="C122" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="E122" s="18">
-        <v>600</v>
-      </c>
-      <c r="F122" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H122" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="I122" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="K122" t="s">
-        <v>121</v>
-      </c>
-      <c r="L122" t="s">
-        <v>191</v>
-      </c>
-      <c r="N122" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="123" spans="1:14">
-      <c r="A123" t="s">
-        <v>229</v>
-      </c>
-      <c r="B123" s="19">
-        <v>1500</v>
-      </c>
-      <c r="C123" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="E123" s="18">
-        <v>2000</v>
-      </c>
-      <c r="F123" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H123" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="I123" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="K123" t="s">
-        <v>121</v>
-      </c>
-      <c r="L123" t="s">
-        <v>191</v>
-      </c>
-      <c r="N123" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="124" spans="1:14">
-      <c r="A124" t="s">
-        <v>229</v>
-      </c>
-      <c r="B124" s="19">
-        <v>2500</v>
-      </c>
-      <c r="C124" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="E124" s="18">
-        <v>100</v>
-      </c>
-      <c r="F124" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H124" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="I124" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="K124" t="s">
-        <v>129</v>
-      </c>
-      <c r="L124" t="s">
-        <v>191</v>
-      </c>
-      <c r="N124" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="125" spans="1:14">
-      <c r="A125" t="s">
-        <v>229</v>
-      </c>
-      <c r="B125" s="19">
-        <v>6000</v>
-      </c>
-      <c r="C125" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="E125" s="18">
-        <v>400</v>
-      </c>
-      <c r="F125" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H125" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="I125" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="K125" t="s">
-        <v>129</v>
-      </c>
-      <c r="L125" t="s">
-        <v>191</v>
-      </c>
-      <c r="N125" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="126" spans="1:14">
-      <c r="A126" t="s">
-        <v>229</v>
-      </c>
-      <c r="B126" s="19">
-        <v>2000</v>
-      </c>
-      <c r="C126" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="E126" s="18">
-        <v>1000</v>
-      </c>
-      <c r="F126" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H126" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="I126" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="K126" t="s">
-        <v>129</v>
-      </c>
-      <c r="L126" t="s">
-        <v>191</v>
-      </c>
-      <c r="N126" t="s">
+        <v>272</v>
+      </c>
+      <c r="M112" t="s">
         <v>243</v>
-      </c>
-    </row>
-    <row r="127" spans="1:14">
-      <c r="A127" t="s">
-        <v>244</v>
-      </c>
-      <c r="B127" s="19">
-        <v>1163849</v>
-      </c>
-      <c r="C127" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="E127" s="18">
-        <v>1000</v>
-      </c>
-      <c r="F127" s="18" t="s">
-        <v>245</v>
-      </c>
-      <c r="H127" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="I127" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="K127" t="s">
-        <v>246</v>
-      </c>
-      <c r="L127" t="s">
-        <v>191</v>
-      </c>
-      <c r="N127" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="128" spans="1:14">
-      <c r="A128" t="s">
-        <v>248</v>
-      </c>
-      <c r="B128" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="C128" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="E128" s="18">
-        <v>180</v>
-      </c>
-      <c r="F128" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="H128" s="15">
-        <v>100</v>
-      </c>
-      <c r="I128" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="K128" t="s">
-        <v>129</v>
-      </c>
-      <c r="L128" t="s">
-        <v>191</v>
-      </c>
-      <c r="N128" t="s">
-        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -6198,34 +5929,34 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4EF6727-D562-4CB5-8104-F2599F2ED213}">
   <dimension ref="A1:S12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.85546875" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="29.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="23.7109375" customWidth="1"/>
-    <col min="19" max="19" width="59.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.88671875" customWidth="1"/>
+    <col min="5" max="5" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="23.6640625" customWidth="1"/>
+    <col min="19" max="19" width="59.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>8</v>
@@ -6279,7 +6010,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>27</v>
       </c>
@@ -6311,149 +6042,149 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="30.75">
+    <row r="3" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>34</v>
       </c>
       <c r="B3" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="C3">
         <v>20</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>29</v>
       </c>
       <c r="F3" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="G3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="30.75">
+    <row r="4" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C4">
         <v>40</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>29</v>
       </c>
       <c r="F4" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="G4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="30.75">
+    <row r="5" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C5">
         <v>6</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>29</v>
       </c>
       <c r="F5" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="G5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="30.75">
+    <row r="6" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C6">
         <v>28</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>29</v>
       </c>
       <c r="F6" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="G6" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="30.75">
+    <row r="7" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C7">
         <v>5</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>29</v>
       </c>
       <c r="F7" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="G7" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="30.75">
+    <row r="8" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C8">
         <v>22</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>29</v>
       </c>
       <c r="F8" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="G8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="45.75">
+    <row r="9" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C9">
         <v>68</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>29</v>
       </c>
       <c r="F9" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="G9" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="45.75">
+    <row r="10" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C10">
         <v>113</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>29</v>
       </c>
       <c r="F10" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="G10" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:19">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="C11">
         <v>34</v>
       </c>
@@ -6461,7 +6192,7 @@
         <v>29</v>
       </c>
       <c r="F11" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="G11" t="s">
         <v>38</v>
@@ -6470,18 +6201,18 @@
         <v>5</v>
       </c>
       <c r="R11" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="C12" s="8">
         <v>200000</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="F12" t="s">
         <v>37</v>
@@ -6493,7 +6224,7 @@
         <v>5</v>
       </c>
       <c r="R12" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
     </row>
   </sheetData>
@@ -6504,74 +6235,74 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{334870B0-CF5C-431A-BCE6-3FF004B4A904}">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="63.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="46.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="63.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="46.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="60.140625" customWidth="1"/>
-    <col min="6" max="6" width="85.5703125" customWidth="1"/>
+    <col min="5" max="5" width="60.109375" customWidth="1"/>
+    <col min="6" max="6" width="85.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="B1" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="C1" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="D1" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="E1" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="F1" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>27</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="D2" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="F2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="60.75">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>34</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="D3" s="7">
         <v>46251</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>44</v>
       </c>

--- a/raw_data/cost_data_collection.xlsx
+++ b/raw_data/cost_data_collection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1d83fea8a85e4500/Documents/JJE/RS/biogas-upgrading-project/raw_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="8_{55BEFA44-F5E8-4583-8C97-582736C20BAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{523B1827-614E-4E1D-A17B-A8B9284ECE08}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="8_{55BEFA44-F5E8-4583-8C97-582736C20BAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07CFED58-4AD0-410B-B4D1-6CBBAC763159}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -636,9 +636,6 @@
     <t>FROM TEXT/TABLE (not a plot) - Table 5-10, page 98 (PDF page 98). MT-Energie amine scrubbing; breakdown: plant 1,482,000 + ancillary construction 74,100; includes 32,000 EUR adsorptive fine desulphurisation. Indicative prices estimated by the supplier from its 600 Nm3/h Godenstedt prototype; no reference plants yet. Excludes the heat-supply boiler (see separate rows) and any investment subsidy. Product gas assumes 0.1% methane loss. Price basis: the report states all investment and operating costs were obtained directly from the suppliers between 2007 and 2008 (p. 84); indicative prices, net before taxes; transport, installation and commissioning included unless stated; rounded up to full 1,000 EUR. Capacity = raw biogas. Product gas figure is the report's own, taken from the same table.</t>
   </si>
   <si>
-    <t>Electrigaz Technologies Inc.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Report has information about different biogas plants starting from 80-81. </t>
   </si>
   <si>
@@ -759,9 +756,6 @@
     <t>FROM TEXT/TABLE (not a plot) - page 11650 (PDF page 20). Text statement: "remains constant at 2000 € per Nm3/h" for 1000 Nm3/h capacity and above; capacity is a threshold. Secondary figure citing Chen et al. 2015 (and Patterson et al. 2011). Cross-check: Bauer 2013 Fig 17 reading (this sheet): curve off-chart (&gt;6000) below ~135; 2722 at 400; 1943 at 1000. No price year stated.</t>
   </si>
   <si>
-    <t>South Coast AQMD (contract 13432) toolkit manual</t>
-  </si>
-  <si>
     <t>scfm</t>
   </si>
   <si>
@@ -862,6 +856,12 @@
   </si>
   <si>
     <t>checked</t>
+  </si>
+  <si>
+    <t>Electrigaz Technologies Inc.2011</t>
+  </si>
+  <si>
+    <t>South Coast AQMD toolkit manual 2014</t>
   </si>
 </sst>
 </file>
@@ -873,7 +873,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -902,6 +902,12 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -2362,7 +2368,7 @@
         <v>72</v>
       </c>
       <c r="L2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M2" t="s">
         <v>110</v>
@@ -2394,7 +2400,7 @@
         <v>72</v>
       </c>
       <c r="L3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M3" t="s">
         <v>111</v>
@@ -2426,7 +2432,7 @@
         <v>72</v>
       </c>
       <c r="L4" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M4" t="s">
         <v>112</v>
@@ -2458,7 +2464,7 @@
         <v>72</v>
       </c>
       <c r="L5" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M5" t="s">
         <v>113</v>
@@ -2490,7 +2496,7 @@
         <v>72</v>
       </c>
       <c r="L6" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M6" t="s">
         <v>114</v>
@@ -2522,7 +2528,7 @@
         <v>72</v>
       </c>
       <c r="L7" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M7" t="s">
         <v>115</v>
@@ -2554,7 +2560,7 @@
         <v>72</v>
       </c>
       <c r="L8" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M8" t="s">
         <v>116</v>
@@ -2586,7 +2592,7 @@
         <v>72</v>
       </c>
       <c r="L9" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M9" t="s">
         <v>117</v>
@@ -2618,7 +2624,7 @@
         <v>72</v>
       </c>
       <c r="L10" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M10" t="s">
         <v>118</v>
@@ -2650,7 +2656,7 @@
         <v>119</v>
       </c>
       <c r="L11" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M11" t="s">
         <v>120</v>
@@ -2682,7 +2688,7 @@
         <v>119</v>
       </c>
       <c r="L12" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M12" t="s">
         <v>121</v>
@@ -2714,7 +2720,7 @@
         <v>119</v>
       </c>
       <c r="L13" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M13" t="s">
         <v>122</v>
@@ -2746,7 +2752,7 @@
         <v>119</v>
       </c>
       <c r="L14" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M14" t="s">
         <v>123</v>
@@ -2778,7 +2784,7 @@
         <v>119</v>
       </c>
       <c r="L15" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M15" t="s">
         <v>124</v>
@@ -2810,7 +2816,7 @@
         <v>119</v>
       </c>
       <c r="L16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M16" t="s">
         <v>125</v>
@@ -2842,7 +2848,7 @@
         <v>119</v>
       </c>
       <c r="L17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M17" t="s">
         <v>126</v>
@@ -2874,7 +2880,7 @@
         <v>127</v>
       </c>
       <c r="L18" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M18" t="s">
         <v>128</v>
@@ -2906,7 +2912,7 @@
         <v>127</v>
       </c>
       <c r="L19" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M19" t="s">
         <v>129</v>
@@ -2938,7 +2944,7 @@
         <v>127</v>
       </c>
       <c r="L20" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M20" t="s">
         <v>130</v>
@@ -2970,7 +2976,7 @@
         <v>127</v>
       </c>
       <c r="L21" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M21" t="s">
         <v>131</v>
@@ -3002,7 +3008,7 @@
         <v>127</v>
       </c>
       <c r="L22" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M22" t="s">
         <v>132</v>
@@ -3034,7 +3040,7 @@
         <v>127</v>
       </c>
       <c r="L23" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M23" t="s">
         <v>133</v>
@@ -3066,7 +3072,7 @@
         <v>127</v>
       </c>
       <c r="L24" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M24" t="s">
         <v>134</v>
@@ -3098,7 +3104,7 @@
         <v>127</v>
       </c>
       <c r="L25" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M25" t="s">
         <v>135</v>
@@ -3130,7 +3136,7 @@
         <v>136</v>
       </c>
       <c r="L26" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M26" t="s">
         <v>137</v>
@@ -3162,7 +3168,7 @@
         <v>136</v>
       </c>
       <c r="L27" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M27" t="s">
         <v>138</v>
@@ -3194,7 +3200,7 @@
         <v>136</v>
       </c>
       <c r="L28" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M28" t="s">
         <v>139</v>
@@ -3226,7 +3232,7 @@
         <v>136</v>
       </c>
       <c r="L29" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M29" t="s">
         <v>140</v>
@@ -3258,7 +3264,7 @@
         <v>136</v>
       </c>
       <c r="L30" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M30" t="s">
         <v>141</v>
@@ -3290,7 +3296,7 @@
         <v>136</v>
       </c>
       <c r="L31" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M31" t="s">
         <v>142</v>
@@ -3322,7 +3328,7 @@
         <v>136</v>
       </c>
       <c r="L32" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M32" t="s">
         <v>143</v>
@@ -3354,7 +3360,7 @@
         <v>144</v>
       </c>
       <c r="L33" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M33" t="s">
         <v>145</v>
@@ -3386,7 +3392,7 @@
         <v>144</v>
       </c>
       <c r="L34" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M34" t="s">
         <v>146</v>
@@ -3418,7 +3424,7 @@
         <v>144</v>
       </c>
       <c r="L35" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M35" t="s">
         <v>147</v>
@@ -3450,7 +3456,7 @@
         <v>144</v>
       </c>
       <c r="L36" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M36" t="s">
         <v>148</v>
@@ -3482,7 +3488,7 @@
         <v>144</v>
       </c>
       <c r="L37" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M37" t="s">
         <v>149</v>
@@ -3514,7 +3520,7 @@
         <v>144</v>
       </c>
       <c r="L38" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M38" t="s">
         <v>150</v>
@@ -3546,7 +3552,7 @@
         <v>144</v>
       </c>
       <c r="L39" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M39" t="s">
         <v>151</v>
@@ -3578,7 +3584,7 @@
         <v>144</v>
       </c>
       <c r="L40" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M40" t="s">
         <v>152</v>
@@ -3610,7 +3616,7 @@
         <v>119</v>
       </c>
       <c r="L41" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M41" t="s">
         <v>154</v>
@@ -3642,7 +3648,7 @@
         <v>119</v>
       </c>
       <c r="L42" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M42" t="s">
         <v>155</v>
@@ -3674,7 +3680,7 @@
         <v>156</v>
       </c>
       <c r="L43" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M43" t="s">
         <v>157</v>
@@ -3706,7 +3712,7 @@
         <v>158</v>
       </c>
       <c r="L44" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M44" t="s">
         <v>159</v>
@@ -3738,7 +3744,7 @@
         <v>158</v>
       </c>
       <c r="L45" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M45" t="s">
         <v>160</v>
@@ -3770,7 +3776,7 @@
         <v>127</v>
       </c>
       <c r="L46" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M46" t="s">
         <v>163</v>
@@ -3802,7 +3808,7 @@
         <v>127</v>
       </c>
       <c r="L47" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M47" t="s">
         <v>163</v>
@@ -3834,7 +3840,7 @@
         <v>127</v>
       </c>
       <c r="L48" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M48" t="s">
         <v>163</v>
@@ -3866,7 +3872,7 @@
         <v>127</v>
       </c>
       <c r="L49" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M49" t="s">
         <v>163</v>
@@ -3898,7 +3904,7 @@
         <v>127</v>
       </c>
       <c r="L50" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M50" t="s">
         <v>163</v>
@@ -3930,7 +3936,7 @@
         <v>127</v>
       </c>
       <c r="L51" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M51" t="s">
         <v>163</v>
@@ -3962,7 +3968,7 @@
         <v>119</v>
       </c>
       <c r="L52" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M52" t="s">
         <v>164</v>
@@ -3994,7 +4000,7 @@
         <v>165</v>
       </c>
       <c r="L53" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M53" t="s">
         <v>166</v>
@@ -4026,7 +4032,7 @@
         <v>165</v>
       </c>
       <c r="L54" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M54" t="s">
         <v>167</v>
@@ -4058,7 +4064,7 @@
         <v>169</v>
       </c>
       <c r="L55" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M55" t="s">
         <v>170</v>
@@ -4090,7 +4096,7 @@
         <v>169</v>
       </c>
       <c r="L56" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M56" t="s">
         <v>171</v>
@@ -4122,7 +4128,7 @@
         <v>173</v>
       </c>
       <c r="L57" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M57" t="s">
         <v>174</v>
@@ -4154,7 +4160,7 @@
         <v>173</v>
       </c>
       <c r="L58" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M58" t="s">
         <v>176</v>
@@ -4186,7 +4192,7 @@
         <v>178</v>
       </c>
       <c r="L59" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M59" t="s">
         <v>179</v>
@@ -4218,7 +4224,7 @@
         <v>178</v>
       </c>
       <c r="L60" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M60" t="s">
         <v>180</v>
@@ -4250,7 +4256,7 @@
         <v>72</v>
       </c>
       <c r="L61" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M61" t="s">
         <v>181</v>
@@ -4282,7 +4288,7 @@
         <v>165</v>
       </c>
       <c r="L62" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M62" t="s">
         <v>182</v>
@@ -4314,7 +4320,7 @@
         <v>119</v>
       </c>
       <c r="L63" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M63" t="s">
         <v>183</v>
@@ -4349,7 +4355,7 @@
         <v>72</v>
       </c>
       <c r="L64" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M64" t="s">
         <v>186</v>
@@ -4384,7 +4390,7 @@
         <v>72</v>
       </c>
       <c r="L65" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M65" t="s">
         <v>187</v>
@@ -4419,7 +4425,7 @@
         <v>72</v>
       </c>
       <c r="L66" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M66" t="s">
         <v>188</v>
@@ -4454,7 +4460,7 @@
         <v>119</v>
       </c>
       <c r="L67" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M67" t="s">
         <v>189</v>
@@ -4489,7 +4495,7 @@
         <v>119</v>
       </c>
       <c r="L68" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M68" t="s">
         <v>190</v>
@@ -4524,7 +4530,7 @@
         <v>119</v>
       </c>
       <c r="L69" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M69" t="s">
         <v>191</v>
@@ -4559,7 +4565,7 @@
         <v>136</v>
       </c>
       <c r="L70" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M70" t="s">
         <v>192</v>
@@ -4594,7 +4600,7 @@
         <v>119</v>
       </c>
       <c r="L71" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M71" t="s">
         <v>193</v>
@@ -4629,7 +4635,7 @@
         <v>136</v>
       </c>
       <c r="L72" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M72" t="s">
         <v>194</v>
@@ -4664,7 +4670,7 @@
         <v>136</v>
       </c>
       <c r="L73" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M73" t="s">
         <v>195</v>
@@ -4699,7 +4705,7 @@
         <v>136</v>
       </c>
       <c r="L74" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M74" t="s">
         <v>196</v>
@@ -4707,7 +4713,7 @@
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>197</v>
+        <v>271</v>
       </c>
       <c r="B75" s="19">
         <v>1977000</v>
@@ -4731,15 +4737,15 @@
         <v>72</v>
       </c>
       <c r="L75" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M75" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>197</v>
+        <v>271</v>
       </c>
       <c r="B76" s="19">
         <v>2030000</v>
@@ -4763,15 +4769,15 @@
         <v>72</v>
       </c>
       <c r="L76" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M76" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>197</v>
+        <v>271</v>
       </c>
       <c r="B77" s="19">
         <v>2896000</v>
@@ -4795,15 +4801,15 @@
         <v>72</v>
       </c>
       <c r="L77" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M77" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>197</v>
+        <v>271</v>
       </c>
       <c r="B78" s="19">
         <v>3713000</v>
@@ -4827,15 +4833,15 @@
         <v>72</v>
       </c>
       <c r="L78" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M78" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>197</v>
+        <v>271</v>
       </c>
       <c r="B79" s="19">
         <v>4163000</v>
@@ -4859,15 +4865,15 @@
         <v>72</v>
       </c>
       <c r="L79" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M79" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>197</v>
+        <v>271</v>
       </c>
       <c r="B80" s="19">
         <v>4405000</v>
@@ -4888,18 +4894,18 @@
         <v>108</v>
       </c>
       <c r="K80" t="s">
+        <v>202</v>
+      </c>
+      <c r="L80" t="s">
+        <v>270</v>
+      </c>
+      <c r="M80" t="s">
         <v>203</v>
-      </c>
-      <c r="L80" t="s">
-        <v>272</v>
-      </c>
-      <c r="M80" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>197</v>
+        <v>271</v>
       </c>
       <c r="B81" s="19">
         <v>6773000</v>
@@ -4920,18 +4926,18 @@
         <v>108</v>
       </c>
       <c r="K81" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L81" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M81" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>197</v>
+        <v>271</v>
       </c>
       <c r="B82" s="19">
         <v>10263000</v>
@@ -4952,18 +4958,18 @@
         <v>108</v>
       </c>
       <c r="K82" t="s">
+        <v>205</v>
+      </c>
+      <c r="L82" t="s">
+        <v>270</v>
+      </c>
+      <c r="M82" t="s">
         <v>206</v>
-      </c>
-      <c r="L82" t="s">
-        <v>272</v>
-      </c>
-      <c r="M82" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B83" s="19">
         <v>5500</v>
@@ -4987,15 +4993,15 @@
         <v>72</v>
       </c>
       <c r="L83" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M83" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B84" s="19">
         <v>2500</v>
@@ -5019,15 +5025,15 @@
         <v>72</v>
       </c>
       <c r="L84" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M84" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B85" s="19">
         <v>1800</v>
@@ -5051,15 +5057,15 @@
         <v>72</v>
       </c>
       <c r="L85" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M85" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B86" s="19">
         <v>2000</v>
@@ -5083,15 +5089,15 @@
         <v>72</v>
       </c>
       <c r="L86" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M86" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B87" s="19">
         <v>4500</v>
@@ -5115,15 +5121,15 @@
         <v>144</v>
       </c>
       <c r="L87" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M87" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B88" s="19">
         <v>2000</v>
@@ -5147,15 +5153,15 @@
         <v>144</v>
       </c>
       <c r="L88" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M88" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B89" s="19">
         <v>1500</v>
@@ -5179,15 +5185,15 @@
         <v>144</v>
       </c>
       <c r="L89" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M89" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B90" s="19">
         <v>3200</v>
@@ -5211,15 +5217,15 @@
         <v>136</v>
       </c>
       <c r="L90" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M90" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B91" s="19">
         <v>1500</v>
@@ -5243,15 +5249,15 @@
         <v>136</v>
       </c>
       <c r="L91" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M91" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B92" s="19">
         <v>2700</v>
@@ -5275,15 +5281,15 @@
         <v>119</v>
       </c>
       <c r="L92" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M92" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B93" s="19">
         <v>1500</v>
@@ -5307,15 +5313,15 @@
         <v>119</v>
       </c>
       <c r="L93" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M93" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B94" s="19">
         <v>6000</v>
@@ -5339,15 +5345,15 @@
         <v>127</v>
       </c>
       <c r="L94" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M94" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B95" s="19">
         <v>2500</v>
@@ -5371,15 +5377,15 @@
         <v>127</v>
       </c>
       <c r="L95" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M95" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B96" s="19">
         <v>2000</v>
@@ -5403,15 +5409,15 @@
         <v>127</v>
       </c>
       <c r="L96" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M96" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B97" s="19">
         <v>5500</v>
@@ -5435,15 +5441,15 @@
         <v>72</v>
       </c>
       <c r="L97" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M97" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B98" s="19">
         <v>2500</v>
@@ -5467,15 +5473,15 @@
         <v>72</v>
       </c>
       <c r="L98" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M98" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B99" s="19">
         <v>1800</v>
@@ -5499,15 +5505,15 @@
         <v>72</v>
       </c>
       <c r="L99" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M99" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B100" s="19">
         <v>2000</v>
@@ -5531,15 +5537,15 @@
         <v>72</v>
       </c>
       <c r="L100" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M100" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B101" s="19">
         <v>4500</v>
@@ -5563,15 +5569,15 @@
         <v>144</v>
       </c>
       <c r="L101" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M101" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B102" s="19">
         <v>2000</v>
@@ -5595,15 +5601,15 @@
         <v>144</v>
       </c>
       <c r="L102" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M102" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B103" s="19">
         <v>1500</v>
@@ -5627,15 +5633,15 @@
         <v>144</v>
       </c>
       <c r="L103" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M103" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B104" s="19">
         <v>3200</v>
@@ -5659,15 +5665,15 @@
         <v>136</v>
       </c>
       <c r="L104" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M104" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B105" s="19">
         <v>1500</v>
@@ -5691,15 +5697,15 @@
         <v>136</v>
       </c>
       <c r="L105" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M105" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B106" s="19">
         <v>2700</v>
@@ -5723,15 +5729,15 @@
         <v>119</v>
       </c>
       <c r="L106" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M106" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B107" s="19">
         <v>1500</v>
@@ -5755,15 +5761,15 @@
         <v>119</v>
       </c>
       <c r="L107" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M107" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B108" s="19">
         <v>2500</v>
@@ -5787,15 +5793,15 @@
         <v>127</v>
       </c>
       <c r="L108" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M108" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B109" s="19">
         <v>6000</v>
@@ -5819,15 +5825,15 @@
         <v>127</v>
       </c>
       <c r="L109" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M109" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B110" s="19">
         <v>2000</v>
@@ -5851,15 +5857,15 @@
         <v>127</v>
       </c>
       <c r="L110" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M110" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>238</v>
+        <v>272</v>
       </c>
       <c r="B111" s="19">
         <v>1163849</v>
@@ -5871,27 +5877,27 @@
         <v>1000</v>
       </c>
       <c r="F111" s="18" t="s">
+        <v>237</v>
+      </c>
+      <c r="H111" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="I111" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="K111" t="s">
+        <v>238</v>
+      </c>
+      <c r="L111" t="s">
+        <v>270</v>
+      </c>
+      <c r="M111" t="s">
         <v>239</v>
-      </c>
-      <c r="H111" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="I111" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="K111" t="s">
-        <v>240</v>
-      </c>
-      <c r="L111" t="s">
-        <v>272</v>
-      </c>
-      <c r="M111" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B112" s="19" t="s">
         <v>109</v>
@@ -5915,13 +5921,14 @@
         <v>127</v>
       </c>
       <c r="L112" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M112" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5956,7 +5963,7 @@
         <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>8</v>
@@ -6047,19 +6054,19 @@
         <v>34</v>
       </c>
       <c r="B3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C3">
         <v>20</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>29</v>
       </c>
       <c r="F3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G3" t="s">
         <v>38</v>
@@ -6070,13 +6077,13 @@
         <v>40</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>29</v>
       </c>
       <c r="F4" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G4" t="s">
         <v>38</v>
@@ -6087,13 +6094,13 @@
         <v>6</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>29</v>
       </c>
       <c r="F5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G5" t="s">
         <v>38</v>
@@ -6104,13 +6111,13 @@
         <v>28</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>29</v>
       </c>
       <c r="F6" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G6" t="s">
         <v>38</v>
@@ -6121,13 +6128,13 @@
         <v>5</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>29</v>
       </c>
       <c r="F7" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G7" t="s">
         <v>38</v>
@@ -6138,13 +6145,13 @@
         <v>22</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>29</v>
       </c>
       <c r="F8" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G8" t="s">
         <v>38</v>
@@ -6155,13 +6162,13 @@
         <v>68</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>29</v>
       </c>
       <c r="F9" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G9" t="s">
         <v>38</v>
@@ -6172,13 +6179,13 @@
         <v>113</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>29</v>
       </c>
       <c r="F10" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G10" t="s">
         <v>38</v>
@@ -6192,7 +6199,7 @@
         <v>29</v>
       </c>
       <c r="F11" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G11" t="s">
         <v>38</v>
@@ -6201,7 +6208,7 @@
         <v>5</v>
       </c>
       <c r="R11" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
@@ -6209,10 +6216,10 @@
         <v>200000</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F12" t="s">
         <v>37</v>
@@ -6224,7 +6231,7 @@
         <v>5</v>
       </c>
       <c r="R12" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
   </sheetData>
@@ -6247,22 +6254,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C1" t="s">
         <v>258</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>259</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>260</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>261</v>
-      </c>
-      <c r="E1" t="s">
-        <v>262</v>
-      </c>
-      <c r="F1" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -6270,19 +6277,19 @@
         <v>27</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="D2" t="s">
         <v>264</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>266</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="F2" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
@@ -6290,16 +6297,16 @@
         <v>34</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D3" s="7">
         <v>46251</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
